--- a/research/traditional_assets/database/data/egypt/egypt_utility_general.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_utility_general.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1095075805734187</v>
+        <v>0.1092960635171285</v>
       </c>
       <c r="C2">
-        <v>539.8733047716769</v>
+        <v>536.8598702825777</v>
       </c>
       <c r="D2">
-        <v>470.8733047716769</v>
+        <v>472.4418702825777</v>
       </c>
       <c r="E2">
-        <v>-145.1</v>
+        <v>-140.518</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.582000000000001</v>
       </c>
       <c r="G2">
         <v>69</v>
@@ -1433,28 +1433,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2304746</v>
       </c>
       <c r="N2">
-        <v>49.86666666666667</v>
+        <v>49.63619206666667</v>
       </c>
       <c r="O2">
-        <v>11.22</v>
+        <v>11.168143215</v>
       </c>
       <c r="P2">
-        <v>38.64666666666668</v>
+        <v>38.46804885166667</v>
       </c>
       <c r="Q2">
-        <v>45.44666666666667</v>
+        <v>45.26804885166668</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1095075805734187</v>
+        <v>0.1100063015324531</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563938</v>
+        <v>0.4476747490941584</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>216.3651294618438</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1092960635171285</v>
+        <v>0.1090845464608384</v>
       </c>
       <c r="C3">
-        <v>536.8598702825777</v>
+        <v>533.8569210818473</v>
       </c>
       <c r="D3">
-        <v>472.4418702825777</v>
+        <v>474.0209210818473</v>
       </c>
       <c r="E3">
-        <v>-140.518</v>
+        <v>-135.936</v>
       </c>
       <c r="F3">
-        <v>4.582000000000001</v>
+        <v>9.164000000000001</v>
       </c>
       <c r="G3">
         <v>69</v>
@@ -1515,28 +1515,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M3">
-        <v>0.2304746</v>
+        <v>0.4609492000000001</v>
       </c>
       <c r="N3">
-        <v>49.63619206666667</v>
+        <v>49.40571746666667</v>
       </c>
       <c r="O3">
-        <v>11.168143215</v>
+        <v>11.11628643</v>
       </c>
       <c r="P3">
-        <v>38.46804885166667</v>
+        <v>38.28943103666667</v>
       </c>
       <c r="Q3">
-        <v>45.26804885166668</v>
+        <v>45.08943103666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1100063015324531</v>
+        <v>0.1105152004702432</v>
       </c>
       <c r="T3">
-        <v>0.4476747490941584</v>
+        <v>0.4512230177041224</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>216.3651294618438</v>
+        <v>108.1825647309219</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1090845464608384</v>
+        <v>0.1088730294045481</v>
       </c>
       <c r="C4">
-        <v>533.8569210818473</v>
+        <v>530.8645626575536</v>
       </c>
       <c r="D4">
-        <v>474.0209210818473</v>
+        <v>475.6105626575535</v>
       </c>
       <c r="E4">
-        <v>-135.936</v>
+        <v>-131.354</v>
       </c>
       <c r="F4">
-        <v>9.164000000000001</v>
+        <v>13.746</v>
       </c>
       <c r="G4">
         <v>69</v>
@@ -1597,28 +1597,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M4">
-        <v>0.4609492000000001</v>
+        <v>0.6914238</v>
       </c>
       <c r="N4">
-        <v>49.40571746666667</v>
+        <v>49.17524286666667</v>
       </c>
       <c r="O4">
-        <v>11.11628643</v>
+        <v>11.064429645</v>
       </c>
       <c r="P4">
-        <v>38.28943103666667</v>
+        <v>38.11081322166667</v>
       </c>
       <c r="Q4">
-        <v>45.08943103666667</v>
+        <v>44.91081322166667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1105152004702432</v>
+        <v>0.1110345921696373</v>
       </c>
       <c r="T4">
-        <v>0.4512230177041224</v>
+        <v>0.4548444464916114</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>108.1825647309219</v>
+        <v>72.12170982061461</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1088730294045481</v>
+        <v>0.108661512348258</v>
       </c>
       <c r="C5">
-        <v>530.8645626575536</v>
+        <v>527.8829019175528</v>
       </c>
       <c r="D5">
-        <v>475.6105626575535</v>
+        <v>477.2109019175528</v>
       </c>
       <c r="E5">
-        <v>-131.354</v>
+        <v>-126.772</v>
       </c>
       <c r="F5">
-        <v>13.746</v>
+        <v>18.328</v>
       </c>
       <c r="G5">
         <v>69</v>
@@ -1679,28 +1679,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M5">
-        <v>0.6914238</v>
+        <v>0.9218984000000001</v>
       </c>
       <c r="N5">
-        <v>49.17524286666667</v>
+        <v>48.94476826666667</v>
       </c>
       <c r="O5">
-        <v>11.064429645</v>
+        <v>11.01257286</v>
       </c>
       <c r="P5">
-        <v>38.11081322166667</v>
+        <v>37.93219540666667</v>
       </c>
       <c r="Q5">
-        <v>44.91081322166667</v>
+        <v>44.73219540666668</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1110345921696373</v>
+        <v>0.1115648045294354</v>
       </c>
       <c r="T5">
-        <v>0.4548444464916114</v>
+        <v>0.4585413217121731</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.12170982061461</v>
+        <v>54.09128236546095</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.108661512348258</v>
+        <v>0.1084499952919678</v>
       </c>
       <c r="C6">
-        <v>527.8829019175528</v>
+        <v>524.9120472134588</v>
       </c>
       <c r="D6">
-        <v>477.2109019175528</v>
+        <v>478.8220472134587</v>
       </c>
       <c r="E6">
-        <v>-126.772</v>
+        <v>-122.19</v>
       </c>
       <c r="F6">
-        <v>18.328</v>
+        <v>22.91</v>
       </c>
       <c r="G6">
         <v>69</v>
@@ -1761,28 +1761,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M6">
-        <v>0.9218984000000001</v>
+        <v>1.152373</v>
       </c>
       <c r="N6">
-        <v>48.94476826666667</v>
+        <v>48.71429366666668</v>
       </c>
       <c r="O6">
-        <v>11.01257286</v>
+        <v>10.960716075</v>
       </c>
       <c r="P6">
-        <v>37.93219540666667</v>
+        <v>37.75357759166668</v>
       </c>
       <c r="Q6">
-        <v>44.73219540666668</v>
+        <v>44.55357759166668</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1115648045294354</v>
+        <v>0.1121061792547029</v>
       </c>
       <c r="T6">
-        <v>0.4585413217121731</v>
+        <v>0.4623160258847466</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.09128236546095</v>
+        <v>43.27302589236876</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1084499952919678</v>
+        <v>0.1082384782356776</v>
       </c>
       <c r="C7">
-        <v>524.9120472134588</v>
+        <v>521.9521083650959</v>
       </c>
       <c r="D7">
-        <v>478.8220472134587</v>
+        <v>480.4441083650959</v>
       </c>
       <c r="E7">
-        <v>-122.19</v>
+        <v>-117.608</v>
       </c>
       <c r="F7">
-        <v>22.91</v>
+        <v>27.492</v>
       </c>
       <c r="G7">
         <v>69</v>
@@ -1843,28 +1843,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M7">
-        <v>1.152373</v>
+        <v>1.3828476</v>
       </c>
       <c r="N7">
-        <v>48.71429366666668</v>
+        <v>48.48381906666668</v>
       </c>
       <c r="O7">
-        <v>10.960716075</v>
+        <v>10.90885929</v>
       </c>
       <c r="P7">
-        <v>37.75357759166668</v>
+        <v>37.57495977666667</v>
       </c>
       <c r="Q7">
-        <v>44.55357759166668</v>
+        <v>44.37495977666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1121061792547029</v>
+        <v>0.1126590725911464</v>
       </c>
       <c r="T7">
-        <v>0.4623160258847466</v>
+        <v>0.4661710429120557</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.27302589236876</v>
+        <v>36.06085491030731</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1082384782356776</v>
+        <v>0.1080269611793874</v>
       </c>
       <c r="C8">
-        <v>521.9521083650959</v>
+        <v>519.0031966854526</v>
       </c>
       <c r="D8">
-        <v>480.4441083650959</v>
+        <v>482.0771966854526</v>
       </c>
       <c r="E8">
-        <v>-117.608</v>
+        <v>-113.026</v>
       </c>
       <c r="F8">
-        <v>27.492</v>
+        <v>32.074</v>
       </c>
       <c r="G8">
         <v>69</v>
@@ -1925,28 +1925,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M8">
-        <v>1.3828476</v>
+        <v>1.6133222</v>
       </c>
       <c r="N8">
-        <v>48.48381906666668</v>
+        <v>48.25334446666668</v>
       </c>
       <c r="O8">
-        <v>10.90885929</v>
+        <v>10.857002505</v>
       </c>
       <c r="P8">
-        <v>37.57495977666667</v>
+        <v>37.39634196166667</v>
       </c>
       <c r="Q8">
-        <v>44.37495977666667</v>
+        <v>44.19634196166668</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1126590725911464</v>
+        <v>0.1132238561068682</v>
       </c>
       <c r="T8">
-        <v>0.4661710429120557</v>
+        <v>0.4701089635313501</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.06085491030731</v>
+        <v>30.90930420883484</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1080269611793874</v>
+        <v>0.1078154441230972</v>
       </c>
       <c r="C9">
-        <v>519.0031966854527</v>
+        <v>516.0654250061452</v>
       </c>
       <c r="D9">
-        <v>482.0771966854526</v>
+        <v>483.7214250061453</v>
       </c>
       <c r="E9">
-        <v>-113.026</v>
+        <v>-108.444</v>
       </c>
       <c r="F9">
-        <v>32.07400000000001</v>
+        <v>36.65600000000001</v>
       </c>
       <c r="G9">
         <v>69</v>
@@ -2007,28 +2007,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M9">
-        <v>1.6133222</v>
+        <v>1.8437968</v>
       </c>
       <c r="N9">
-        <v>48.25334446666668</v>
+        <v>48.02286986666667</v>
       </c>
       <c r="O9">
-        <v>10.857002505</v>
+        <v>10.80514572</v>
       </c>
       <c r="P9">
-        <v>37.39634196166667</v>
+        <v>37.21772414666667</v>
       </c>
       <c r="Q9">
-        <v>44.19634196166668</v>
+        <v>44.01772414666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1132238561068682</v>
+        <v>0.1138009175251057</v>
       </c>
       <c r="T9">
-        <v>0.4701089635313501</v>
+        <v>0.4741324911206289</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.90930420883483</v>
+        <v>27.04564118273048</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1078154441230972</v>
+        <v>0.107603927066807</v>
       </c>
       <c r="C10">
-        <v>516.0654250061452</v>
+        <v>513.138907703405</v>
       </c>
       <c r="D10">
-        <v>483.7214250061453</v>
+        <v>485.376907703405</v>
       </c>
       <c r="E10">
-        <v>-108.444</v>
+        <v>-103.862</v>
       </c>
       <c r="F10">
-        <v>36.65600000000001</v>
+        <v>41.238</v>
       </c>
       <c r="G10">
         <v>69</v>
@@ -2089,28 +2089,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M10">
-        <v>1.8437968</v>
+        <v>2.0742714</v>
       </c>
       <c r="N10">
-        <v>48.02286986666667</v>
+        <v>47.79239526666667</v>
       </c>
       <c r="O10">
-        <v>10.80514572</v>
+        <v>10.753288935</v>
       </c>
       <c r="P10">
-        <v>37.21772414666667</v>
+        <v>37.03910633166667</v>
       </c>
       <c r="Q10">
-        <v>44.01772414666667</v>
+        <v>43.83910633166667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1138009175251057</v>
+        <v>0.1143906616118758</v>
       </c>
       <c r="T10">
-        <v>0.4741324911206289</v>
+        <v>0.4782444478876943</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.04564118273048</v>
+        <v>24.04056994020487</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.107603927066807</v>
+        <v>0.1073924100105168</v>
       </c>
       <c r="C11">
-        <v>513.138907703405</v>
+        <v>510.2237607245992</v>
       </c>
       <c r="D11">
-        <v>485.376907703405</v>
+        <v>487.0437607245992</v>
       </c>
       <c r="E11">
-        <v>-103.862</v>
+        <v>-99.28</v>
       </c>
       <c r="F11">
-        <v>41.238</v>
+        <v>45.82</v>
       </c>
       <c r="G11">
         <v>69</v>
@@ -2171,28 +2171,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M11">
-        <v>2.0742714</v>
+        <v>2.304746</v>
       </c>
       <c r="N11">
-        <v>47.79239526666667</v>
+        <v>47.56192066666667</v>
       </c>
       <c r="O11">
-        <v>10.753288935</v>
+        <v>10.70143215</v>
       </c>
       <c r="P11">
-        <v>37.03910633166667</v>
+        <v>36.86048851666667</v>
       </c>
       <c r="Q11">
-        <v>43.83910633166667</v>
+        <v>43.66048851666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1143906616118758</v>
+        <v>0.1149935111227965</v>
       </c>
       <c r="T11">
-        <v>0.4782444478876943</v>
+        <v>0.4824477814718054</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.04056994020487</v>
+        <v>21.63651294618439</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1073924100105168</v>
+        <v>0.1071808929542266</v>
       </c>
       <c r="C12">
-        <v>510.2237607245992</v>
+        <v>507.3201016153026</v>
       </c>
       <c r="D12">
-        <v>487.0437607245992</v>
+        <v>488.7221016153026</v>
       </c>
       <c r="E12">
-        <v>-99.27999999999999</v>
+        <v>-94.69799999999998</v>
       </c>
       <c r="F12">
-        <v>45.82000000000001</v>
+        <v>50.40200000000001</v>
       </c>
       <c r="G12">
         <v>69</v>
@@ -2253,28 +2253,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M12">
-        <v>2.304746</v>
+        <v>2.5352206</v>
       </c>
       <c r="N12">
-        <v>47.56192066666667</v>
+        <v>47.33144606666667</v>
       </c>
       <c r="O12">
-        <v>10.70143215</v>
+        <v>10.649575365</v>
       </c>
       <c r="P12">
-        <v>36.86048851666667</v>
+        <v>36.68187070166667</v>
       </c>
       <c r="Q12">
-        <v>43.66048851666667</v>
+        <v>43.48187070166667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1149935111227965</v>
+        <v>0.1156099078137378</v>
       </c>
       <c r="T12">
-        <v>0.4824477814718054</v>
+        <v>0.486745571990391</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.63651294618438</v>
+        <v>19.66955722380398</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1071808929542266</v>
+        <v>0.1069693758979364</v>
       </c>
       <c r="C13">
-        <v>507.3201016153026</v>
+        <v>504.4280495469297</v>
       </c>
       <c r="D13">
-        <v>488.7221016153026</v>
+        <v>490.4120495469296</v>
       </c>
       <c r="E13">
-        <v>-94.69799999999998</v>
+        <v>-90.11599999999999</v>
       </c>
       <c r="F13">
-        <v>50.40200000000001</v>
+        <v>54.984</v>
       </c>
       <c r="G13">
         <v>69</v>
@@ -2335,28 +2335,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M13">
-        <v>2.5352206</v>
+        <v>2.7656952</v>
       </c>
       <c r="N13">
-        <v>47.33144606666667</v>
+        <v>47.10097146666667</v>
       </c>
       <c r="O13">
-        <v>10.649575365</v>
+        <v>10.59771858</v>
       </c>
       <c r="P13">
-        <v>36.68187070166667</v>
+        <v>36.50325288666667</v>
       </c>
       <c r="Q13">
-        <v>43.48187070166667</v>
+        <v>43.30325288666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1156099078137378</v>
+        <v>0.1162403135203823</v>
       </c>
       <c r="T13">
-        <v>0.486745571990391</v>
+        <v>0.4911410395662172</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.66955722380398</v>
+        <v>18.03042745515365</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1069693758979364</v>
+        <v>0.1067578588416462</v>
       </c>
       <c r="C14">
-        <v>504.4280495469297</v>
+        <v>501.5477253449407</v>
       </c>
       <c r="D14">
-        <v>490.4120495469296</v>
+        <v>492.1137253449407</v>
       </c>
       <c r="E14">
-        <v>-90.11599999999999</v>
+        <v>-85.53399999999999</v>
       </c>
       <c r="F14">
-        <v>54.984</v>
+        <v>59.56600000000001</v>
       </c>
       <c r="G14">
         <v>69</v>
@@ -2417,28 +2417,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M14">
-        <v>2.7656952</v>
+        <v>2.996169800000001</v>
       </c>
       <c r="N14">
-        <v>47.10097146666667</v>
+        <v>46.87049686666667</v>
       </c>
       <c r="O14">
-        <v>10.59771858</v>
+        <v>10.545861795</v>
       </c>
       <c r="P14">
-        <v>36.50325288666667</v>
+        <v>36.32463507166667</v>
       </c>
       <c r="Q14">
-        <v>43.30325288666667</v>
+        <v>43.12463507166667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1162403135203823</v>
+        <v>0.1168852113122371</v>
       </c>
       <c r="T14">
-        <v>0.4911410395662172</v>
+        <v>0.4956375523736716</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.03042745515365</v>
+        <v>16.64347149706491</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1067578588416462</v>
+        <v>0.1065463417853561</v>
       </c>
       <c r="C15">
-        <v>501.5477253449407</v>
+        <v>498.6792515176402</v>
       </c>
       <c r="D15">
-        <v>492.1137253449407</v>
+        <v>493.8272515176401</v>
       </c>
       <c r="E15">
-        <v>-85.53399999999999</v>
+        <v>-80.95199999999998</v>
       </c>
       <c r="F15">
-        <v>59.56600000000001</v>
+        <v>64.14800000000001</v>
       </c>
       <c r="G15">
         <v>69</v>
@@ -2499,28 +2499,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M15">
-        <v>2.996169800000001</v>
+        <v>3.226644400000001</v>
       </c>
       <c r="N15">
-        <v>46.87049686666667</v>
+        <v>46.64002226666668</v>
       </c>
       <c r="O15">
-        <v>10.545861795</v>
+        <v>10.49400501</v>
       </c>
       <c r="P15">
-        <v>36.32463507166667</v>
+        <v>36.14601725666667</v>
       </c>
       <c r="Q15">
-        <v>43.12463507166667</v>
+        <v>42.94601725666668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1168852113122371</v>
+        <v>0.1175451067271582</v>
       </c>
       <c r="T15">
-        <v>0.4956375523736716</v>
+        <v>0.5002386352464155</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.64347149706491</v>
+        <v>15.45465210441742</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1065463417853561</v>
+        <v>0.1063348247290659</v>
       </c>
       <c r="C16">
-        <v>498.6792515176402</v>
+        <v>495.8227522855763</v>
       </c>
       <c r="D16">
-        <v>493.8272515176401</v>
+        <v>495.5527522855763</v>
       </c>
       <c r="E16">
-        <v>-80.95199999999998</v>
+        <v>-76.36999999999998</v>
       </c>
       <c r="F16">
-        <v>64.14800000000001</v>
+        <v>68.73000000000002</v>
       </c>
       <c r="G16">
         <v>69</v>
@@ -2581,28 +2581,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M16">
-        <v>3.226644400000001</v>
+        <v>3.457119000000001</v>
       </c>
       <c r="N16">
-        <v>46.64002226666668</v>
+        <v>46.40954766666668</v>
       </c>
       <c r="O16">
-        <v>10.49400501</v>
+        <v>10.442148225</v>
       </c>
       <c r="P16">
-        <v>36.14601725666667</v>
+        <v>35.96739944166667</v>
       </c>
       <c r="Q16">
-        <v>42.94601725666668</v>
+        <v>42.76739944166667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1175451067271582</v>
+        <v>0.1182205290930187</v>
       </c>
       <c r="T16">
-        <v>0.5002386352464155</v>
+        <v>0.5049479788926359</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.45465210441742</v>
+        <v>14.42434196412292</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1063348247290659</v>
+        <v>0.1061233076727756</v>
       </c>
       <c r="C17">
-        <v>495.8227522855763</v>
+        <v>492.9783536115605</v>
       </c>
       <c r="D17">
-        <v>495.5527522855763</v>
+        <v>497.2903536115605</v>
       </c>
       <c r="E17">
-        <v>-76.36999999999999</v>
+        <v>-71.78799999999998</v>
       </c>
       <c r="F17">
-        <v>68.73</v>
+        <v>73.31200000000001</v>
       </c>
       <c r="G17">
         <v>69</v>
@@ -2663,28 +2663,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M17">
-        <v>3.457119</v>
+        <v>3.6875936</v>
       </c>
       <c r="N17">
-        <v>46.40954766666668</v>
+        <v>46.17907306666667</v>
       </c>
       <c r="O17">
-        <v>10.442148225</v>
+        <v>10.39029144</v>
       </c>
       <c r="P17">
-        <v>35.96739944166667</v>
+        <v>35.78878162666668</v>
       </c>
       <c r="Q17">
-        <v>42.76739944166667</v>
+        <v>42.58878162666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1182205290930187</v>
+        <v>0.1189120329437805</v>
       </c>
       <c r="T17">
-        <v>0.5049479788926359</v>
+        <v>0.509769449768528</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.42434196412292</v>
+        <v>13.52282059136524</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1061233076727756</v>
+        <v>0.1061094156164855</v>
       </c>
       <c r="C18">
-        <v>492.9783536115605</v>
+        <v>488.5109026502855</v>
       </c>
       <c r="D18">
-        <v>497.2903536115605</v>
+        <v>497.4049026502856</v>
       </c>
       <c r="E18">
-        <v>-71.78799999999998</v>
+        <v>-67.20599999999997</v>
       </c>
       <c r="F18">
-        <v>73.31200000000001</v>
+        <v>77.89400000000002</v>
       </c>
       <c r="G18">
         <v>69</v>
@@ -2745,45 +2745,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M18">
-        <v>3.6875936</v>
+        <v>4.034909200000001</v>
       </c>
       <c r="N18">
-        <v>46.17907306666667</v>
+        <v>45.83175746666667</v>
       </c>
       <c r="O18">
-        <v>10.39029144</v>
+        <v>10.31214543</v>
       </c>
       <c r="P18">
-        <v>35.78878162666668</v>
+        <v>35.51961203666667</v>
       </c>
       <c r="Q18">
-        <v>42.58878162666667</v>
+        <v>42.31961203666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1189120329437805</v>
+        <v>0.1196201995379343</v>
       </c>
       <c r="T18">
-        <v>0.509769449768528</v>
+        <v>0.5147071006655262</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.225</v>
       </c>
       <c r="W18">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.52282059136524</v>
+        <v>12.358807644709</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1061094156164855</v>
+        <v>0.1059095235601953</v>
       </c>
       <c r="C19">
-        <v>488.5109026502855</v>
+        <v>485.5830047444407</v>
       </c>
       <c r="D19">
-        <v>497.4049026502856</v>
+        <v>499.0590047444407</v>
       </c>
       <c r="E19">
-        <v>-67.20599999999997</v>
+        <v>-62.62399999999998</v>
       </c>
       <c r="F19">
-        <v>77.89400000000002</v>
+        <v>82.47600000000001</v>
       </c>
       <c r="G19">
         <v>69</v>
@@ -2827,28 +2827,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M19">
-        <v>4.034909200000001</v>
+        <v>4.272256800000001</v>
       </c>
       <c r="N19">
-        <v>45.83175746666667</v>
+        <v>45.59440986666667</v>
       </c>
       <c r="O19">
-        <v>10.31214543</v>
+        <v>10.25874222</v>
       </c>
       <c r="P19">
-        <v>35.51961203666667</v>
+        <v>35.33566764666667</v>
       </c>
       <c r="Q19">
-        <v>42.31961203666667</v>
+        <v>42.13566764666668</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1196201995379343</v>
+        <v>0.120345638488043</v>
       </c>
       <c r="T19">
-        <v>0.5147071006655262</v>
+        <v>0.5197651820722071</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.358807644709</v>
+        <v>11.67220722000294</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1059095235601953</v>
+        <v>0.1057096315039051</v>
       </c>
       <c r="C20">
-        <v>485.5830047444405</v>
+        <v>482.666144859048</v>
       </c>
       <c r="D20">
-        <v>499.0590047444405</v>
+        <v>500.7241448590481</v>
       </c>
       <c r="E20">
-        <v>-62.624</v>
+        <v>-58.04199999999999</v>
       </c>
       <c r="F20">
-        <v>82.476</v>
+        <v>87.05800000000001</v>
       </c>
       <c r="G20">
         <v>69</v>
@@ -2909,28 +2909,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M20">
-        <v>4.2722568</v>
+        <v>4.509604400000001</v>
       </c>
       <c r="N20">
-        <v>45.59440986666667</v>
+        <v>45.35706226666667</v>
       </c>
       <c r="O20">
-        <v>10.25874222</v>
+        <v>10.20533901</v>
       </c>
       <c r="P20">
-        <v>35.33566764666667</v>
+        <v>35.15172325666667</v>
       </c>
       <c r="Q20">
-        <v>42.13566764666668</v>
+        <v>41.95172325666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.120345638488043</v>
+        <v>0.1210889895109939</v>
       </c>
       <c r="T20">
-        <v>0.5197651820722071</v>
+        <v>0.5249481543778184</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.67220722000294</v>
+        <v>11.05788052421331</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1057096315039051</v>
+        <v>0.1055097394476149</v>
       </c>
       <c r="C21">
-        <v>482.666144859048</v>
+        <v>479.7604338510281</v>
       </c>
       <c r="D21">
-        <v>500.7241448590481</v>
+        <v>502.400433851028</v>
       </c>
       <c r="E21">
-        <v>-58.04199999999999</v>
+        <v>-53.45999999999998</v>
       </c>
       <c r="F21">
-        <v>87.05800000000001</v>
+        <v>91.64000000000001</v>
       </c>
       <c r="G21">
         <v>69</v>
@@ -2991,28 +2991,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M21">
-        <v>4.509604400000001</v>
+        <v>4.746952</v>
       </c>
       <c r="N21">
-        <v>45.35706226666667</v>
+        <v>45.11971466666667</v>
       </c>
       <c r="O21">
-        <v>10.20533901</v>
+        <v>10.1519358</v>
       </c>
       <c r="P21">
-        <v>35.15172325666667</v>
+        <v>34.96777886666667</v>
       </c>
       <c r="Q21">
-        <v>41.95172325666667</v>
+        <v>41.76777886666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1210889895109939</v>
+        <v>0.1218509243095186</v>
       </c>
       <c r="T21">
-        <v>0.5249481543778184</v>
+        <v>0.53026070099107</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.05788052421331</v>
+        <v>10.50498649800265</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1055097394476149</v>
+        <v>0.1053098473913247</v>
       </c>
       <c r="C22">
-        <v>479.7604338510281</v>
+        <v>476.8659840667626</v>
       </c>
       <c r="D22">
-        <v>502.400433851028</v>
+        <v>504.0879840667625</v>
       </c>
       <c r="E22">
-        <v>-53.45999999999998</v>
+        <v>-48.87799999999997</v>
       </c>
       <c r="F22">
-        <v>91.64000000000001</v>
+        <v>96.22200000000002</v>
       </c>
       <c r="G22">
         <v>69</v>
@@ -3073,28 +3073,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M22">
-        <v>4.746952</v>
+        <v>4.984299600000001</v>
       </c>
       <c r="N22">
-        <v>45.11971466666667</v>
+        <v>44.88236706666667</v>
       </c>
       <c r="O22">
-        <v>10.1519358</v>
+        <v>10.09853259</v>
       </c>
       <c r="P22">
-        <v>34.96777886666667</v>
+        <v>34.78383447666667</v>
       </c>
       <c r="Q22">
-        <v>41.76777886666667</v>
+        <v>41.58383447666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1218509243095186</v>
+        <v>0.1226321485966135</v>
       </c>
       <c r="T22">
-        <v>0.53026070099107</v>
+        <v>0.5357077424552901</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.50498649800265</v>
+        <v>10.00474904571681</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1053098473913247</v>
+        <v>0.1053998053350345</v>
       </c>
       <c r="C23">
-        <v>476.8659840667626</v>
+        <v>471.5231306002025</v>
       </c>
       <c r="D23">
-        <v>504.0879840667625</v>
+        <v>503.3271306002025</v>
       </c>
       <c r="E23">
-        <v>-48.87799999999999</v>
+        <v>-44.29599999999998</v>
       </c>
       <c r="F23">
-        <v>96.22200000000001</v>
+        <v>100.804</v>
       </c>
       <c r="G23">
         <v>69</v>
@@ -3155,45 +3155,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M23">
-        <v>4.9842996</v>
+        <v>5.393014000000001</v>
       </c>
       <c r="N23">
-        <v>44.88236706666667</v>
+        <v>44.47365266666667</v>
       </c>
       <c r="O23">
-        <v>10.09853259</v>
+        <v>10.00657185</v>
       </c>
       <c r="P23">
-        <v>34.78383447666667</v>
+        <v>34.46708081666667</v>
       </c>
       <c r="Q23">
-        <v>41.58383447666667</v>
+        <v>41.26708081666668</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1226321485966135</v>
+        <v>0.1234334042756853</v>
       </c>
       <c r="T23">
-        <v>0.5357077424552901</v>
+        <v>0.541294451649362</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.225</v>
       </c>
       <c r="W23">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.00474904571681</v>
+        <v>9.246530171563927</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1053998053350345</v>
+        <v>0.1052130882787443</v>
       </c>
       <c r="C24">
-        <v>471.5231306002025</v>
+        <v>468.5229329084033</v>
       </c>
       <c r="D24">
-        <v>503.3271306002025</v>
+        <v>504.9089329084034</v>
       </c>
       <c r="E24">
-        <v>-44.29599999999998</v>
+        <v>-39.71399999999998</v>
       </c>
       <c r="F24">
-        <v>100.804</v>
+        <v>105.386</v>
       </c>
       <c r="G24">
         <v>69</v>
@@ -3237,28 +3237,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M24">
-        <v>5.393014000000001</v>
+        <v>5.638151000000001</v>
       </c>
       <c r="N24">
-        <v>44.47365266666667</v>
+        <v>44.22851566666667</v>
       </c>
       <c r="O24">
-        <v>10.00657185</v>
+        <v>9.951416025000002</v>
       </c>
       <c r="P24">
-        <v>34.46708081666667</v>
+        <v>34.27709964166667</v>
       </c>
       <c r="Q24">
-        <v>41.26708081666668</v>
+        <v>41.07709964166668</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1234334042756853</v>
+        <v>0.124255471790577</v>
       </c>
       <c r="T24">
-        <v>0.541294451649362</v>
+        <v>0.5470262701731499</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.246530171563927</v>
+        <v>8.844507120626368</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1052130882787443</v>
+        <v>0.1050263712224541</v>
       </c>
       <c r="C25">
-        <v>468.5229329084033</v>
+        <v>465.5327087964309</v>
       </c>
       <c r="D25">
-        <v>504.9089329084034</v>
+        <v>506.5007087964309</v>
       </c>
       <c r="E25">
-        <v>-39.71399999999998</v>
+        <v>-35.13199999999998</v>
       </c>
       <c r="F25">
-        <v>105.386</v>
+        <v>109.968</v>
       </c>
       <c r="G25">
         <v>69</v>
@@ -3319,28 +3319,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M25">
-        <v>5.638151000000001</v>
+        <v>5.883288000000001</v>
       </c>
       <c r="N25">
-        <v>44.22851566666667</v>
+        <v>43.98337866666667</v>
       </c>
       <c r="O25">
-        <v>9.951416025000002</v>
+        <v>9.896260200000002</v>
       </c>
       <c r="P25">
-        <v>34.27709964166667</v>
+        <v>34.08711846666667</v>
       </c>
       <c r="Q25">
-        <v>41.07709964166668</v>
+        <v>40.88711846666668</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.124255471790577</v>
+        <v>0.1250991726611239</v>
       </c>
       <c r="T25">
-        <v>0.5470262701731499</v>
+        <v>0.5529089260265112</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.844507120626368</v>
+        <v>8.475985990600268</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1050263712224541</v>
+        <v>0.1048396541661639</v>
       </c>
       <c r="C26">
-        <v>465.5327087964309</v>
+        <v>462.5525528907273</v>
       </c>
       <c r="D26">
-        <v>506.5007087964309</v>
+        <v>508.1025528907273</v>
       </c>
       <c r="E26">
-        <v>-35.13199999999999</v>
+        <v>-30.54999999999998</v>
       </c>
       <c r="F26">
-        <v>109.968</v>
+        <v>114.55</v>
       </c>
       <c r="G26">
         <v>69</v>
@@ -3401,28 +3401,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M26">
-        <v>5.883288</v>
+        <v>6.128425000000001</v>
       </c>
       <c r="N26">
-        <v>43.98337866666667</v>
+        <v>43.73824166666667</v>
       </c>
       <c r="O26">
-        <v>9.896260200000002</v>
+        <v>9.841104375000002</v>
       </c>
       <c r="P26">
-        <v>34.08711846666667</v>
+        <v>33.89713729166667</v>
       </c>
       <c r="Q26">
-        <v>40.88711846666668</v>
+        <v>40.69713729166668</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1250991726611239</v>
+        <v>0.1259653722215519</v>
       </c>
       <c r="T26">
-        <v>0.5529089260265112</v>
+        <v>0.5589484527026288</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.475985990600268</v>
+        <v>8.136946550976257</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1048396541661639</v>
+        <v>0.1046529371098738</v>
       </c>
       <c r="C27">
-        <v>462.5525528907273</v>
+        <v>459.5825610185828</v>
       </c>
       <c r="D27">
-        <v>508.1025528907273</v>
+        <v>509.7145610185829</v>
       </c>
       <c r="E27">
-        <v>-30.54999999999998</v>
+        <v>-25.96799999999998</v>
       </c>
       <c r="F27">
-        <v>114.55</v>
+        <v>119.132</v>
       </c>
       <c r="G27">
         <v>69</v>
@@ -3483,28 +3483,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M27">
-        <v>6.128425000000001</v>
+        <v>6.373562000000001</v>
       </c>
       <c r="N27">
-        <v>43.73824166666667</v>
+        <v>43.49310466666667</v>
       </c>
       <c r="O27">
-        <v>9.841104375000002</v>
+        <v>9.785948550000002</v>
       </c>
       <c r="P27">
-        <v>33.89713729166667</v>
+        <v>33.70715611666667</v>
       </c>
       <c r="Q27">
-        <v>40.69713729166668</v>
+        <v>40.50715611666668</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1259653722215519</v>
+        <v>0.1268549825809105</v>
       </c>
       <c r="T27">
-        <v>0.5589484527026288</v>
+        <v>0.5651512098294524</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.136946550976257</v>
+        <v>7.823987068246401</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1046529371098738</v>
+        <v>0.1046336200535836</v>
       </c>
       <c r="C28">
-        <v>459.5825610185828</v>
+        <v>455.1679174528489</v>
       </c>
       <c r="D28">
-        <v>509.7145610185829</v>
+        <v>509.8819174528489</v>
       </c>
       <c r="E28">
-        <v>-25.96799999999998</v>
+        <v>-21.38599999999997</v>
       </c>
       <c r="F28">
-        <v>119.132</v>
+        <v>123.714</v>
       </c>
       <c r="G28">
         <v>69</v>
@@ -3565,45 +3565,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M28">
-        <v>6.373562000000001</v>
+        <v>6.717670200000001</v>
       </c>
       <c r="N28">
-        <v>43.49310466666667</v>
+        <v>43.14899646666667</v>
       </c>
       <c r="O28">
-        <v>9.785948550000002</v>
+        <v>9.708524205000002</v>
       </c>
       <c r="P28">
-        <v>33.70715611666667</v>
+        <v>33.44047226166667</v>
       </c>
       <c r="Q28">
-        <v>40.50715611666668</v>
+        <v>40.24047226166667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1268549825809105</v>
+        <v>0.1277689658268268</v>
       </c>
       <c r="T28">
-        <v>0.5651512098294524</v>
+        <v>0.5715239055076957</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.225</v>
       </c>
       <c r="W28">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.823987068246401</v>
+        <v>7.423208520517525</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1046336200535836</v>
+        <v>0.1044531029972934</v>
       </c>
       <c r="C29">
-        <v>455.1679174528489</v>
+        <v>452.1551845178569</v>
       </c>
       <c r="D29">
-        <v>509.8819174528489</v>
+        <v>511.451184517857</v>
       </c>
       <c r="E29">
-        <v>-21.38599999999997</v>
+        <v>-16.80399999999997</v>
       </c>
       <c r="F29">
-        <v>123.714</v>
+        <v>128.296</v>
       </c>
       <c r="G29">
         <v>69</v>
@@ -3647,28 +3647,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M29">
-        <v>6.717670200000001</v>
+        <v>6.966472800000001</v>
       </c>
       <c r="N29">
-        <v>43.14899646666667</v>
+        <v>42.90019386666668</v>
       </c>
       <c r="O29">
-        <v>9.708524205000002</v>
+        <v>9.652543620000003</v>
       </c>
       <c r="P29">
-        <v>33.44047226166667</v>
+        <v>33.24765024666667</v>
       </c>
       <c r="Q29">
-        <v>40.24047226166667</v>
+        <v>40.04765024666668</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1277689658268268</v>
+        <v>0.1287083374962408</v>
       </c>
       <c r="T29">
-        <v>0.5715239055076957</v>
+        <v>0.5780736205103346</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.423208520517525</v>
+        <v>7.158093930499042</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1044531029972934</v>
+        <v>0.1042725859410032</v>
       </c>
       <c r="C30">
-        <v>452.1551845178569</v>
+        <v>449.152140891677</v>
       </c>
       <c r="D30">
-        <v>511.451184517857</v>
+        <v>513.0301408916771</v>
       </c>
       <c r="E30">
-        <v>-16.80399999999997</v>
+        <v>-12.22199999999995</v>
       </c>
       <c r="F30">
-        <v>128.296</v>
+        <v>132.878</v>
       </c>
       <c r="G30">
         <v>69</v>
@@ -3729,28 +3729,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M30">
-        <v>6.966472800000001</v>
+        <v>7.215275400000002</v>
       </c>
       <c r="N30">
-        <v>42.90019386666668</v>
+        <v>42.65139126666667</v>
       </c>
       <c r="O30">
-        <v>9.652543620000003</v>
+        <v>9.596563035000001</v>
       </c>
       <c r="P30">
-        <v>33.24765024666667</v>
+        <v>33.05482823166667</v>
       </c>
       <c r="Q30">
-        <v>40.04765024666668</v>
+        <v>39.85482823166667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1287083374962408</v>
+        <v>0.1296741703394411</v>
       </c>
       <c r="T30">
-        <v>0.5780736205103346</v>
+        <v>0.5848078345271326</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.158093930499042</v>
+        <v>6.911263105309419</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1042725859410032</v>
+        <v>0.104092068884713</v>
       </c>
       <c r="C31">
-        <v>449.1521408916773</v>
+        <v>446.1588765909552</v>
       </c>
       <c r="D31">
-        <v>513.0301408916773</v>
+        <v>514.6188765909552</v>
       </c>
       <c r="E31">
-        <v>-12.22199999999998</v>
+        <v>-7.639999999999986</v>
       </c>
       <c r="F31">
-        <v>132.878</v>
+        <v>137.46</v>
       </c>
       <c r="G31">
         <v>69</v>
@@ -3811,28 +3811,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M31">
-        <v>7.215275400000001</v>
+        <v>7.464078000000001</v>
       </c>
       <c r="N31">
-        <v>42.65139126666667</v>
+        <v>42.40258866666667</v>
       </c>
       <c r="O31">
-        <v>9.596563035000001</v>
+        <v>9.540582450000002</v>
       </c>
       <c r="P31">
-        <v>33.05482823166667</v>
+        <v>32.86200621666667</v>
       </c>
       <c r="Q31">
-        <v>39.85482823166667</v>
+        <v>39.66200621666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1296741703394411</v>
+        <v>0.1306675984067328</v>
       </c>
       <c r="T31">
-        <v>0.5848078345271325</v>
+        <v>0.591734454658696</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.91126310530942</v>
+        <v>6.680887668465773</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.104092068884713</v>
+        <v>0.1039115518284228</v>
       </c>
       <c r="C32">
-        <v>446.1588765909552</v>
+        <v>443.1754827508431</v>
       </c>
       <c r="D32">
-        <v>514.6188765909552</v>
+        <v>516.2174827508431</v>
       </c>
       <c r="E32">
-        <v>-7.639999999999986</v>
+        <v>-3.057999999999993</v>
       </c>
       <c r="F32">
-        <v>137.46</v>
+        <v>142.042</v>
       </c>
       <c r="G32">
         <v>69</v>
@@ -3893,28 +3893,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M32">
-        <v>7.464078000000001</v>
+        <v>7.7128806</v>
       </c>
       <c r="N32">
-        <v>42.40258866666667</v>
+        <v>42.15378606666668</v>
       </c>
       <c r="O32">
-        <v>9.540582450000002</v>
+        <v>9.484601865000002</v>
       </c>
       <c r="P32">
-        <v>32.86200621666667</v>
+        <v>32.66918420166667</v>
       </c>
       <c r="Q32">
-        <v>39.66200621666667</v>
+        <v>39.46918420166668</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1306675984067328</v>
+        <v>0.1316898214904678</v>
       </c>
       <c r="T32">
-        <v>0.591734454658696</v>
+        <v>0.5988618463882758</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.680887668465773</v>
+        <v>6.465375163031394</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1039115518284228</v>
+        <v>0.1037310347721326</v>
       </c>
       <c r="C33">
-        <v>443.1754827508431</v>
+        <v>440.202051642427</v>
       </c>
       <c r="D33">
-        <v>516.2174827508431</v>
+        <v>517.826051642427</v>
       </c>
       <c r="E33">
-        <v>-3.057999999999993</v>
+        <v>1.524000000000029</v>
       </c>
       <c r="F33">
-        <v>142.042</v>
+        <v>146.624</v>
       </c>
       <c r="G33">
         <v>69</v>
@@ -3975,28 +3975,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M33">
-        <v>7.7128806</v>
+        <v>7.961683200000001</v>
       </c>
       <c r="N33">
-        <v>42.15378606666668</v>
+        <v>41.90498346666667</v>
       </c>
       <c r="O33">
-        <v>9.484601865000002</v>
+        <v>9.428621280000002</v>
       </c>
       <c r="P33">
-        <v>32.66918420166667</v>
+        <v>32.47636218666667</v>
       </c>
       <c r="Q33">
-        <v>39.46918420166668</v>
+        <v>39.27636218666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1316898214904678</v>
+        <v>0.1327421099590185</v>
       </c>
       <c r="T33">
-        <v>0.5988618463882758</v>
+        <v>0.6061988672863726</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.465375163031394</v>
+        <v>6.263332189186661</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1037310347721326</v>
+        <v>0.1038062677158424</v>
       </c>
       <c r="C34">
-        <v>440.202051642427</v>
+        <v>434.9484418366465</v>
       </c>
       <c r="D34">
-        <v>517.826051642427</v>
+        <v>517.1544418366465</v>
       </c>
       <c r="E34">
-        <v>1.524000000000029</v>
+        <v>6.106000000000023</v>
       </c>
       <c r="F34">
-        <v>146.624</v>
+        <v>151.206</v>
       </c>
       <c r="G34">
         <v>69</v>
@@ -4057,45 +4057,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M34">
-        <v>7.961683200000001</v>
+        <v>8.361691800000001</v>
       </c>
       <c r="N34">
-        <v>41.90498346666667</v>
+        <v>41.50497486666667</v>
       </c>
       <c r="O34">
-        <v>9.428621280000002</v>
+        <v>9.338619345000001</v>
       </c>
       <c r="P34">
-        <v>32.47636218666667</v>
+        <v>32.16635552166667</v>
       </c>
       <c r="Q34">
-        <v>39.27636218666667</v>
+        <v>38.96635552166667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1327421099590185</v>
+        <v>0.1338258100236454</v>
       </c>
       <c r="T34">
-        <v>0.6061988672863726</v>
+        <v>0.6137549037336666</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.225</v>
       </c>
       <c r="W34">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.263332189186661</v>
+        <v>5.963705415053287</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1038062677158424</v>
+        <v>0.1036335006595522</v>
       </c>
       <c r="C35">
-        <v>434.9484418366465</v>
+        <v>431.9113465984984</v>
       </c>
       <c r="D35">
-        <v>517.1544418366465</v>
+        <v>518.6993465984984</v>
       </c>
       <c r="E35">
-        <v>6.106000000000023</v>
+        <v>10.68800000000005</v>
       </c>
       <c r="F35">
-        <v>151.206</v>
+        <v>155.788</v>
       </c>
       <c r="G35">
         <v>69</v>
@@ -4139,28 +4139,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M35">
-        <v>8.361691800000001</v>
+        <v>8.615076400000003</v>
       </c>
       <c r="N35">
-        <v>41.50497486666667</v>
+        <v>41.25159026666667</v>
       </c>
       <c r="O35">
-        <v>9.338619345000001</v>
+        <v>9.281607810000001</v>
       </c>
       <c r="P35">
-        <v>32.16635552166667</v>
+        <v>31.96998245666667</v>
       </c>
       <c r="Q35">
-        <v>38.96635552166667</v>
+        <v>38.76998245666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1338258100236454</v>
+        <v>0.13494234948417</v>
       </c>
       <c r="T35">
-        <v>0.6137549037336666</v>
+        <v>0.6215399109823935</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.963705415053287</v>
+        <v>5.788302314610542</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1036335006595522</v>
+        <v>0.103460733603262</v>
       </c>
       <c r="C36">
-        <v>431.9113465984984</v>
+        <v>428.883509260182</v>
       </c>
       <c r="D36">
-        <v>518.6993465984984</v>
+        <v>520.253509260182</v>
       </c>
       <c r="E36">
-        <v>10.68800000000005</v>
+        <v>15.27000000000004</v>
       </c>
       <c r="F36">
-        <v>155.788</v>
+        <v>160.37</v>
       </c>
       <c r="G36">
         <v>69</v>
@@ -4221,28 +4221,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M36">
-        <v>8.615076400000003</v>
+        <v>8.868461000000002</v>
       </c>
       <c r="N36">
-        <v>41.25159026666667</v>
+        <v>40.99820566666667</v>
       </c>
       <c r="O36">
-        <v>9.281607810000001</v>
+        <v>9.224596275000001</v>
       </c>
       <c r="P36">
-        <v>31.96998245666667</v>
+        <v>31.77360939166667</v>
       </c>
       <c r="Q36">
-        <v>38.76998245666667</v>
+        <v>38.57360939166666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.13494234948417</v>
+        <v>0.1360932440050185</v>
       </c>
       <c r="T36">
-        <v>0.6215399109823935</v>
+        <v>0.6295644569156966</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.788302314610542</v>
+        <v>5.622922248478813</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.103460733603262</v>
+        <v>0.1032879665469718</v>
       </c>
       <c r="C37">
-        <v>428.883509260182</v>
+        <v>425.8650132892571</v>
       </c>
       <c r="D37">
-        <v>520.253509260182</v>
+        <v>521.8170132892571</v>
       </c>
       <c r="E37">
-        <v>15.27000000000004</v>
+        <v>19.85200000000003</v>
       </c>
       <c r="F37">
-        <v>160.37</v>
+        <v>164.952</v>
       </c>
       <c r="G37">
         <v>69</v>
@@ -4303,28 +4303,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M37">
-        <v>8.868461000000002</v>
+        <v>9.121845600000002</v>
       </c>
       <c r="N37">
-        <v>40.99820566666667</v>
+        <v>40.74482106666667</v>
       </c>
       <c r="O37">
-        <v>9.224596275000001</v>
+        <v>9.167584740000002</v>
       </c>
       <c r="P37">
-        <v>31.77360939166667</v>
+        <v>31.57723632666667</v>
       </c>
       <c r="Q37">
-        <v>38.57360939166666</v>
+        <v>38.37723632666668</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1360932440050185</v>
+        <v>0.1372801039796435</v>
       </c>
       <c r="T37">
-        <v>0.6295644569156966</v>
+        <v>0.6378397699094155</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.622922248478813</v>
+        <v>5.466729963798846</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1032879665469718</v>
+        <v>0.1031151994906816</v>
       </c>
       <c r="C38">
-        <v>425.865013289257</v>
+        <v>422.8559431596796</v>
       </c>
       <c r="D38">
-        <v>521.817013289257</v>
+        <v>523.3899431596795</v>
       </c>
       <c r="E38">
-        <v>19.852</v>
+        <v>24.43400000000003</v>
       </c>
       <c r="F38">
-        <v>164.952</v>
+        <v>169.534</v>
       </c>
       <c r="G38">
         <v>69</v>
@@ -4385,28 +4385,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M38">
-        <v>9.1218456</v>
+        <v>9.375230200000001</v>
       </c>
       <c r="N38">
-        <v>40.74482106666667</v>
+        <v>40.49143646666667</v>
       </c>
       <c r="O38">
-        <v>9.167584740000002</v>
+        <v>9.110573205000001</v>
       </c>
       <c r="P38">
-        <v>31.57723632666667</v>
+        <v>31.38086326166667</v>
       </c>
       <c r="Q38">
-        <v>38.37723632666668</v>
+        <v>38.18086326166667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1372801039796435</v>
+        <v>0.138504642048701</v>
       </c>
       <c r="T38">
-        <v>0.6378397699094155</v>
+        <v>0.6463777912521413</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.466729963798847</v>
+        <v>5.318980505317796</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1031151994906816</v>
+        <v>0.1029424324343914</v>
       </c>
       <c r="C39">
-        <v>422.8559431596796</v>
+        <v>419.8563843670157</v>
       </c>
       <c r="D39">
-        <v>523.3899431596795</v>
+        <v>524.9723843670157</v>
       </c>
       <c r="E39">
-        <v>24.43400000000003</v>
+        <v>29.01600000000002</v>
       </c>
       <c r="F39">
-        <v>169.534</v>
+        <v>174.116</v>
       </c>
       <c r="G39">
         <v>69</v>
@@ -4467,28 +4467,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M39">
-        <v>9.375230200000001</v>
+        <v>9.628614800000001</v>
       </c>
       <c r="N39">
-        <v>40.49143646666667</v>
+        <v>40.23805186666667</v>
       </c>
       <c r="O39">
-        <v>9.110573205000001</v>
+        <v>9.053561670000002</v>
       </c>
       <c r="P39">
-        <v>31.38086326166667</v>
+        <v>31.18449019666667</v>
       </c>
       <c r="Q39">
-        <v>38.18086326166667</v>
+        <v>37.98449019666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.138504642048701</v>
+        <v>0.1397686813457926</v>
       </c>
       <c r="T39">
-        <v>0.6463777912521413</v>
+        <v>0.6551912326381808</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.318980505317796</v>
+        <v>5.179007334125223</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1029424324343914</v>
+        <v>0.1027696653781012</v>
       </c>
       <c r="C40">
-        <v>419.8563843670157</v>
+        <v>416.866423443931</v>
       </c>
       <c r="D40">
-        <v>524.9723843670157</v>
+        <v>526.564423443931</v>
       </c>
       <c r="E40">
-        <v>29.01600000000002</v>
+        <v>33.59800000000004</v>
       </c>
       <c r="F40">
-        <v>174.116</v>
+        <v>178.698</v>
       </c>
       <c r="G40">
         <v>69</v>
@@ -4549,28 +4549,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M40">
-        <v>9.628614800000001</v>
+        <v>9.881999400000002</v>
       </c>
       <c r="N40">
-        <v>40.23805186666667</v>
+        <v>39.98466726666668</v>
       </c>
       <c r="O40">
-        <v>9.053561670000002</v>
+        <v>8.996550135000003</v>
       </c>
       <c r="P40">
-        <v>31.18449019666667</v>
+        <v>30.98811713166667</v>
       </c>
       <c r="Q40">
-        <v>37.98449019666667</v>
+        <v>37.78811713166667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1397686813457926</v>
+        <v>0.1410741645542643</v>
       </c>
       <c r="T40">
-        <v>0.6551912326381808</v>
+        <v>0.664293639315566</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.179007334125223</v>
+        <v>5.046212274275859</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1027696653781012</v>
+        <v>0.102596898321811</v>
       </c>
       <c r="C41">
-        <v>416.866423443931</v>
+        <v>413.8861479759663</v>
       </c>
       <c r="D41">
-        <v>526.564423443931</v>
+        <v>528.1661479759663</v>
       </c>
       <c r="E41">
-        <v>33.59800000000004</v>
+        <v>38.18000000000004</v>
       </c>
       <c r="F41">
-        <v>178.698</v>
+        <v>183.28</v>
       </c>
       <c r="G41">
         <v>69</v>
@@ -4631,28 +4631,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M41">
-        <v>9.881999400000002</v>
+        <v>10.135384</v>
       </c>
       <c r="N41">
-        <v>39.98466726666668</v>
+        <v>39.73128266666667</v>
       </c>
       <c r="O41">
-        <v>8.996550135000003</v>
+        <v>8.939538600000002</v>
       </c>
       <c r="P41">
-        <v>30.98811713166667</v>
+        <v>30.79174406666667</v>
       </c>
       <c r="Q41">
-        <v>37.78811713166667</v>
+        <v>37.59174406666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1410741645542643</v>
+        <v>0.1424231638696851</v>
       </c>
       <c r="T41">
-        <v>0.664293639315566</v>
+        <v>0.6736994595488638</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.046212274275859</v>
+        <v>4.920056967418962</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.102596898321811</v>
+        <v>0.1024241312655209</v>
       </c>
       <c r="C42">
-        <v>413.8861479759663</v>
+        <v>410.9156466175975</v>
       </c>
       <c r="D42">
-        <v>528.1661479759663</v>
+        <v>529.7776466175975</v>
       </c>
       <c r="E42">
-        <v>38.18000000000004</v>
+        <v>42.76200000000003</v>
       </c>
       <c r="F42">
-        <v>183.28</v>
+        <v>187.862</v>
       </c>
       <c r="G42">
         <v>69</v>
@@ -4713,28 +4713,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M42">
-        <v>10.135384</v>
+        <v>10.3887686</v>
       </c>
       <c r="N42">
-        <v>39.73128266666667</v>
+        <v>39.47789806666667</v>
       </c>
       <c r="O42">
-        <v>8.939538600000002</v>
+        <v>8.882527065000001</v>
       </c>
       <c r="P42">
-        <v>30.79174406666667</v>
+        <v>30.59537100166667</v>
       </c>
       <c r="Q42">
-        <v>37.59174406666667</v>
+        <v>37.39537100166667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1424231638696851</v>
+        <v>0.1438178919754591</v>
       </c>
       <c r="T42">
-        <v>0.6736994595488638</v>
+        <v>0.6834241211460025</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.920056967418962</v>
+        <v>4.800055577969719</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1024241312655209</v>
+        <v>0.1022513642092307</v>
       </c>
       <c r="C43">
-        <v>410.9156466175975</v>
+        <v>407.9550091085945</v>
       </c>
       <c r="D43">
-        <v>529.7776466175975</v>
+        <v>531.3990091085946</v>
       </c>
       <c r="E43">
-        <v>42.76200000000003</v>
+        <v>47.34400000000005</v>
       </c>
       <c r="F43">
-        <v>187.862</v>
+        <v>192.444</v>
       </c>
       <c r="G43">
         <v>69</v>
@@ -4795,28 +4795,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M43">
-        <v>10.3887686</v>
+        <v>10.6421532</v>
       </c>
       <c r="N43">
-        <v>39.47789806666667</v>
+        <v>39.22451346666667</v>
       </c>
       <c r="O43">
-        <v>8.882527065000001</v>
+        <v>8.825515530000001</v>
       </c>
       <c r="P43">
-        <v>30.59537100166667</v>
+        <v>30.39899793666667</v>
       </c>
       <c r="Q43">
-        <v>37.39537100166667</v>
+        <v>37.19899793666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1438178919754591</v>
+        <v>0.145260714153846</v>
       </c>
       <c r="T43">
-        <v>0.6834241211460025</v>
+        <v>0.693484115901663</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.800055577969719</v>
+        <v>4.68576854039901</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1022513642092307</v>
+        <v>0.1020785971529405</v>
       </c>
       <c r="C44">
-        <v>407.9550091085945</v>
+        <v>405.0043262906792</v>
       </c>
       <c r="D44">
-        <v>531.3990091085946</v>
+        <v>533.0303262906792</v>
       </c>
       <c r="E44">
-        <v>47.34400000000002</v>
+        <v>51.92600000000002</v>
       </c>
       <c r="F44">
-        <v>192.444</v>
+        <v>197.026</v>
       </c>
       <c r="G44">
         <v>69</v>
@@ -4877,28 +4877,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M44">
-        <v>10.6421532</v>
+        <v>10.8955378</v>
       </c>
       <c r="N44">
-        <v>39.22451346666667</v>
+        <v>38.97112886666667</v>
       </c>
       <c r="O44">
-        <v>8.825515530000001</v>
+        <v>8.768503995000001</v>
       </c>
       <c r="P44">
-        <v>30.39899793666667</v>
+        <v>30.20262487166667</v>
       </c>
       <c r="Q44">
-        <v>37.19899793666667</v>
+        <v>37.00262487166667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.145260714153846</v>
+        <v>0.1467541616718254</v>
       </c>
       <c r="T44">
-        <v>0.693484115901663</v>
+        <v>0.7038970929294521</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.685768540399011</v>
+        <v>4.576797178994383</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1020785971529405</v>
+        <v>0.1027583300966503</v>
       </c>
       <c r="C45">
-        <v>405.0043262906792</v>
+        <v>394.0612150684689</v>
       </c>
       <c r="D45">
-        <v>533.0303262906792</v>
+        <v>526.6692150684689</v>
       </c>
       <c r="E45">
-        <v>51.92600000000002</v>
+        <v>56.50800000000004</v>
       </c>
       <c r="F45">
-        <v>197.026</v>
+        <v>201.608</v>
       </c>
       <c r="G45">
         <v>69</v>
@@ -4959,45 +4959,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M45">
-        <v>10.8955378</v>
+        <v>11.6529424</v>
       </c>
       <c r="N45">
-        <v>38.97112886666667</v>
+        <v>38.21372426666667</v>
       </c>
       <c r="O45">
-        <v>8.768503995000001</v>
+        <v>8.598087960000003</v>
       </c>
       <c r="P45">
-        <v>30.20262487166667</v>
+        <v>29.61563630666667</v>
       </c>
       <c r="Q45">
-        <v>37.00262487166667</v>
+        <v>36.41563630666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1467541616718254</v>
+        <v>0.1483009466011612</v>
       </c>
       <c r="T45">
-        <v>0.7038970929294521</v>
+        <v>0.7146819619939478</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.225</v>
       </c>
       <c r="W45">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.576797178994383</v>
+        <v>4.279319759331057</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1027583300966503</v>
+        <v>0.1026049380403601</v>
       </c>
       <c r="C46">
-        <v>394.0612150684689</v>
+        <v>390.9013955455728</v>
       </c>
       <c r="D46">
-        <v>526.6692150684689</v>
+        <v>528.0913955455728</v>
       </c>
       <c r="E46">
-        <v>56.50800000000004</v>
+        <v>61.09000000000003</v>
       </c>
       <c r="F46">
-        <v>201.608</v>
+        <v>206.19</v>
       </c>
       <c r="G46">
         <v>69</v>
@@ -5041,28 +5041,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M46">
-        <v>11.6529424</v>
+        <v>11.917782</v>
       </c>
       <c r="N46">
-        <v>38.21372426666667</v>
+        <v>37.94888466666667</v>
       </c>
       <c r="O46">
-        <v>8.598087960000003</v>
+        <v>8.538499050000002</v>
       </c>
       <c r="P46">
-        <v>29.61563630666667</v>
+        <v>29.41038561666667</v>
       </c>
       <c r="Q46">
-        <v>36.41563630666667</v>
+        <v>36.21038561666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1483009466011612</v>
+        <v>0.1499039782552002</v>
       </c>
       <c r="T46">
-        <v>0.7146819619939478</v>
+        <v>0.7258590081153343</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.279319759331057</v>
+        <v>4.184223764679255</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1026049380403601</v>
+        <v>0.1024515459840699</v>
       </c>
       <c r="C47">
-        <v>390.9013955455728</v>
+        <v>387.7492775314001</v>
       </c>
       <c r="D47">
-        <v>528.0913955455728</v>
+        <v>529.5212775314002</v>
       </c>
       <c r="E47">
-        <v>61.09000000000003</v>
+        <v>65.67200000000003</v>
       </c>
       <c r="F47">
-        <v>206.19</v>
+        <v>210.772</v>
       </c>
       <c r="G47">
         <v>69</v>
@@ -5123,28 +5123,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M47">
-        <v>11.917782</v>
+        <v>12.1826216</v>
       </c>
       <c r="N47">
-        <v>37.94888466666667</v>
+        <v>37.68404506666667</v>
       </c>
       <c r="O47">
-        <v>8.538499050000002</v>
+        <v>8.478910140000002</v>
       </c>
       <c r="P47">
-        <v>29.41038561666667</v>
+        <v>29.20513492666667</v>
       </c>
       <c r="Q47">
-        <v>36.21038561666667</v>
+        <v>36.00513492666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1499039782552002</v>
+        <v>0.1515663814519813</v>
       </c>
       <c r="T47">
-        <v>0.7258590081153343</v>
+        <v>0.7374500189078833</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.184223764679255</v>
+        <v>4.093262378490575</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1024515459840699</v>
+        <v>0.1022981539277797</v>
       </c>
       <c r="C48">
-        <v>387.7492775314001</v>
+        <v>384.6049237545631</v>
       </c>
       <c r="D48">
-        <v>529.5212775314002</v>
+        <v>530.9589237545631</v>
       </c>
       <c r="E48">
-        <v>65.67200000000003</v>
+        <v>70.25400000000005</v>
       </c>
       <c r="F48">
-        <v>210.772</v>
+        <v>215.354</v>
       </c>
       <c r="G48">
         <v>69</v>
@@ -5205,28 +5205,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M48">
-        <v>12.1826216</v>
+        <v>12.4474612</v>
       </c>
       <c r="N48">
-        <v>37.68404506666667</v>
+        <v>37.41920546666667</v>
       </c>
       <c r="O48">
-        <v>8.478910140000002</v>
+        <v>8.419321230000001</v>
       </c>
       <c r="P48">
-        <v>29.20513492666667</v>
+        <v>28.99988423666667</v>
       </c>
       <c r="Q48">
-        <v>36.00513492666667</v>
+        <v>35.79988423666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1515663814519813</v>
+        <v>0.1532915168448674</v>
       </c>
       <c r="T48">
-        <v>0.7374500189078833</v>
+        <v>0.7494784263341134</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.093262378490575</v>
+        <v>4.00617168958652</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1022981539277797</v>
+        <v>0.1034467618714895</v>
       </c>
       <c r="C49">
-        <v>384.6049237545631</v>
+        <v>369.4436020752698</v>
       </c>
       <c r="D49">
-        <v>530.9589237545631</v>
+        <v>520.3796020752699</v>
       </c>
       <c r="E49">
-        <v>70.25400000000005</v>
+        <v>74.83600000000004</v>
       </c>
       <c r="F49">
-        <v>215.354</v>
+        <v>219.936</v>
       </c>
       <c r="G49">
         <v>69</v>
@@ -5287,45 +5287,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M49">
-        <v>12.4474612</v>
+        <v>13.4820768</v>
       </c>
       <c r="N49">
-        <v>37.41920546666667</v>
+        <v>36.38458986666667</v>
       </c>
       <c r="O49">
-        <v>8.419321230000001</v>
+        <v>8.186532720000002</v>
       </c>
       <c r="P49">
-        <v>28.99988423666667</v>
+        <v>28.19805714666667</v>
       </c>
       <c r="Q49">
-        <v>35.79988423666667</v>
+        <v>34.99805714666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1532915168448674</v>
+        <v>0.1550830035990183</v>
       </c>
       <c r="T49">
-        <v>0.7494784263341134</v>
+        <v>0.7619694648151986</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.225</v>
       </c>
       <c r="W49">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.00617168958652</v>
+        <v>3.698737769144489</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1034467618714895</v>
+        <v>0.1033204948151993</v>
       </c>
       <c r="C50">
-        <v>369.44360207527</v>
+        <v>366.0039218817774</v>
       </c>
       <c r="D50">
-        <v>520.37960207527</v>
+        <v>521.5219218817774</v>
       </c>
       <c r="E50">
-        <v>74.83600000000001</v>
+        <v>79.41800000000003</v>
       </c>
       <c r="F50">
-        <v>219.936</v>
+        <v>224.518</v>
       </c>
       <c r="G50">
         <v>69</v>
@@ -5369,28 +5369,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M50">
-        <v>13.4820768</v>
+        <v>13.7629534</v>
       </c>
       <c r="N50">
-        <v>36.38458986666667</v>
+        <v>36.10371326666667</v>
       </c>
       <c r="O50">
-        <v>8.186532720000002</v>
+        <v>8.123335485000002</v>
       </c>
       <c r="P50">
-        <v>28.19805714666667</v>
+        <v>27.98037778166667</v>
       </c>
       <c r="Q50">
-        <v>34.99805714666667</v>
+        <v>34.78037778166667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1550830035990183</v>
+        <v>0.1569447447356849</v>
       </c>
       <c r="T50">
-        <v>0.7619694648151986</v>
+        <v>0.7749503479426006</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.698737769144489</v>
+        <v>3.623253324876234</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1033204948151993</v>
+        <v>0.1031942277589091</v>
       </c>
       <c r="C51">
-        <v>366.0039218817774</v>
+        <v>362.5692678856896</v>
       </c>
       <c r="D51">
-        <v>521.5219218817774</v>
+        <v>522.6692678856896</v>
       </c>
       <c r="E51">
-        <v>79.41800000000003</v>
+        <v>84.00000000000003</v>
       </c>
       <c r="F51">
-        <v>224.518</v>
+        <v>229.1</v>
       </c>
       <c r="G51">
         <v>69</v>
@@ -5451,28 +5451,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M51">
-        <v>13.7629534</v>
+        <v>14.04383</v>
       </c>
       <c r="N51">
-        <v>36.10371326666667</v>
+        <v>35.82283666666667</v>
       </c>
       <c r="O51">
-        <v>8.123335485000002</v>
+        <v>8.060138250000001</v>
       </c>
       <c r="P51">
-        <v>27.98037778166667</v>
+        <v>27.76269841666667</v>
       </c>
       <c r="Q51">
-        <v>34.78037778166667</v>
+        <v>34.56269841666668</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1569447447356849</v>
+        <v>0.1588809555178183</v>
       </c>
       <c r="T51">
-        <v>0.7749503479426006</v>
+        <v>0.7884504663950989</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.623253324876234</v>
+        <v>3.550788258378709</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1031942277589091</v>
+        <v>0.1041746607026189</v>
       </c>
       <c r="C52">
-        <v>362.5692678856896</v>
+        <v>349.2087642895766</v>
       </c>
       <c r="D52">
-        <v>522.6692678856896</v>
+        <v>513.8907642895766</v>
       </c>
       <c r="E52">
-        <v>84.00000000000003</v>
+        <v>88.58200000000002</v>
       </c>
       <c r="F52">
-        <v>229.1</v>
+        <v>233.682</v>
       </c>
       <c r="G52">
         <v>69</v>
@@ -5533,45 +5533,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M52">
-        <v>14.04383</v>
+        <v>14.9790162</v>
       </c>
       <c r="N52">
-        <v>35.82283666666667</v>
+        <v>34.88765046666667</v>
       </c>
       <c r="O52">
-        <v>8.060138250000001</v>
+        <v>7.849721355000001</v>
       </c>
       <c r="P52">
-        <v>27.76269841666667</v>
+        <v>27.03792911166667</v>
       </c>
       <c r="Q52">
-        <v>34.56269841666668</v>
+        <v>33.83792911166667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1588809555178183</v>
+        <v>0.1608961953114672</v>
       </c>
       <c r="T52">
-        <v>0.7884504663950989</v>
+        <v>0.8025016100905563</v>
       </c>
       <c r="U52">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.225</v>
       </c>
       <c r="W52">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.550788258378709</v>
+        <v>3.329101591242465</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1041746607026189</v>
+        <v>0.1040700936463287</v>
       </c>
       <c r="C53">
-        <v>349.2087642895766</v>
+        <v>345.5489533768747</v>
       </c>
       <c r="D53">
-        <v>513.8907642895766</v>
+        <v>514.8129533768747</v>
       </c>
       <c r="E53">
-        <v>88.58200000000002</v>
+        <v>93.16400000000004</v>
       </c>
       <c r="F53">
-        <v>233.682</v>
+        <v>238.264</v>
       </c>
       <c r="G53">
         <v>69</v>
@@ -5615,28 +5615,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M53">
-        <v>14.9790162</v>
+        <v>15.2727224</v>
       </c>
       <c r="N53">
-        <v>34.88765046666667</v>
+        <v>34.59394426666667</v>
       </c>
       <c r="O53">
-        <v>7.849721355000001</v>
+        <v>7.78363746</v>
       </c>
       <c r="P53">
-        <v>27.03792911166667</v>
+        <v>26.81030680666667</v>
       </c>
       <c r="Q53">
-        <v>33.83792911166667</v>
+        <v>33.61030680666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1608961953114672</v>
+        <v>0.1629954034298516</v>
       </c>
       <c r="T53">
-        <v>0.8025016100905563</v>
+        <v>0.8171382181066578</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.329101591242465</v>
+        <v>3.265080406795494</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1040700936463287</v>
+        <v>0.1039655265900385</v>
       </c>
       <c r="C54">
-        <v>345.5489533768747</v>
+        <v>341.8924581944293</v>
       </c>
       <c r="D54">
-        <v>514.8129533768747</v>
+        <v>515.7384581944293</v>
       </c>
       <c r="E54">
-        <v>93.16400000000004</v>
+        <v>97.74600000000004</v>
       </c>
       <c r="F54">
-        <v>238.264</v>
+        <v>242.846</v>
       </c>
       <c r="G54">
         <v>69</v>
@@ -5697,28 +5697,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M54">
-        <v>15.2727224</v>
+        <v>15.5664286</v>
       </c>
       <c r="N54">
-        <v>34.59394426666667</v>
+        <v>34.30023806666667</v>
       </c>
       <c r="O54">
-        <v>7.78363746</v>
+        <v>7.717553565000001</v>
       </c>
       <c r="P54">
-        <v>26.81030680666667</v>
+        <v>26.58268450166667</v>
       </c>
       <c r="Q54">
-        <v>33.61030680666667</v>
+        <v>33.38268450166667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1629954034298516</v>
+        <v>0.1651839395532735</v>
       </c>
       <c r="T54">
-        <v>0.8171382181066578</v>
+        <v>0.8323976605064231</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.265080406795494</v>
+        <v>3.20347511610124</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1039655265900385</v>
+        <v>0.1038609595337484</v>
       </c>
       <c r="C55">
-        <v>341.8924581944293</v>
+        <v>338.2392966570056</v>
       </c>
       <c r="D55">
-        <v>515.7384581944293</v>
+        <v>516.6672966570056</v>
       </c>
       <c r="E55">
-        <v>97.74600000000004</v>
+        <v>102.3280000000001</v>
       </c>
       <c r="F55">
-        <v>242.846</v>
+        <v>247.4280000000001</v>
       </c>
       <c r="G55">
         <v>69</v>
@@ -5779,28 +5779,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M55">
-        <v>15.5664286</v>
+        <v>15.8601348</v>
       </c>
       <c r="N55">
-        <v>34.30023806666667</v>
+        <v>34.00653186666667</v>
       </c>
       <c r="O55">
-        <v>7.717553565000001</v>
+        <v>7.651469670000001</v>
       </c>
       <c r="P55">
-        <v>26.58268450166667</v>
+        <v>26.35506219666667</v>
       </c>
       <c r="Q55">
-        <v>33.38268450166667</v>
+        <v>33.15506219666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1651839395532735</v>
+        <v>0.1674676294211921</v>
       </c>
       <c r="T55">
-        <v>0.8323976605064231</v>
+        <v>0.8483205569235694</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.20347511610124</v>
+        <v>3.144151502840106</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1038609595337484</v>
+        <v>0.1037563924774582</v>
       </c>
       <c r="C56">
-        <v>338.2392966570056</v>
+        <v>334.5894868086587</v>
       </c>
       <c r="D56">
-        <v>516.6672966570056</v>
+        <v>517.5994868086588</v>
       </c>
       <c r="E56">
-        <v>102.3280000000001</v>
+        <v>106.9100000000001</v>
       </c>
       <c r="F56">
-        <v>247.4280000000001</v>
+        <v>252.01</v>
       </c>
       <c r="G56">
         <v>69</v>
@@ -5861,28 +5861,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M56">
-        <v>15.8601348</v>
+        <v>16.153841</v>
       </c>
       <c r="N56">
-        <v>34.00653186666667</v>
+        <v>33.71282566666667</v>
       </c>
       <c r="O56">
-        <v>7.651469670000001</v>
+        <v>7.585385775000002</v>
       </c>
       <c r="P56">
-        <v>26.35506219666667</v>
+        <v>26.12743989166667</v>
       </c>
       <c r="Q56">
-        <v>33.15506219666667</v>
+        <v>32.92743989166667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1674676294211921</v>
+        <v>0.1698528166165737</v>
       </c>
       <c r="T56">
-        <v>0.8483205569235694</v>
+        <v>0.8649511376259224</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.144151502840106</v>
+        <v>3.086985111879377</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1037563924774582</v>
+        <v>0.103651825421168</v>
       </c>
       <c r="C57">
-        <v>334.5894868086587</v>
+        <v>330.9430468239023</v>
       </c>
       <c r="D57">
-        <v>517.5994868086588</v>
+        <v>518.5350468239023</v>
       </c>
       <c r="E57">
-        <v>106.9100000000001</v>
+        <v>111.492</v>
       </c>
       <c r="F57">
-        <v>252.01</v>
+        <v>256.592</v>
       </c>
       <c r="G57">
         <v>69</v>
@@ -5943,28 +5943,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M57">
-        <v>16.153841</v>
+        <v>16.4475472</v>
       </c>
       <c r="N57">
-        <v>33.71282566666667</v>
+        <v>33.41911946666667</v>
       </c>
       <c r="O57">
-        <v>7.585385775000002</v>
+        <v>7.519301880000001</v>
       </c>
       <c r="P57">
-        <v>26.12743989166667</v>
+        <v>25.89981758666667</v>
       </c>
       <c r="Q57">
-        <v>32.92743989166667</v>
+        <v>32.69981758666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1698528166165737</v>
+        <v>0.1723464214117454</v>
       </c>
       <c r="T57">
-        <v>0.8649511376259224</v>
+        <v>0.8823376538147458</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.086985111879377</v>
+        <v>3.031860377738674</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.103651825421168</v>
+        <v>0.1069929083648778</v>
       </c>
       <c r="C58">
-        <v>330.9430468239023</v>
+        <v>298.0494557106178</v>
       </c>
       <c r="D58">
-        <v>518.5350468239023</v>
+        <v>490.2234557106178</v>
       </c>
       <c r="E58">
-        <v>111.492</v>
+        <v>116.074</v>
       </c>
       <c r="F58">
-        <v>256.592</v>
+        <v>261.174</v>
       </c>
       <c r="G58">
         <v>69</v>
@@ -6025,45 +6025,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M58">
-        <v>16.4475472</v>
+        <v>18.7784106</v>
       </c>
       <c r="N58">
-        <v>33.41911946666667</v>
+        <v>31.08825606666667</v>
       </c>
       <c r="O58">
-        <v>7.519301880000001</v>
+        <v>6.994857615000001</v>
       </c>
       <c r="P58">
-        <v>25.89981758666667</v>
+        <v>24.09339845166667</v>
       </c>
       <c r="Q58">
-        <v>32.69981758666667</v>
+        <v>30.89339845166667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1723464214117454</v>
+        <v>0.1749560078252972</v>
       </c>
       <c r="T58">
-        <v>0.8823376538147458</v>
+        <v>0.9005328451751425</v>
       </c>
       <c r="U58">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V58">
         <v>0.225</v>
       </c>
       <c r="W58">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.031860377738674</v>
+        <v>2.655531808781871</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1069929083648778</v>
+        <v>0.1069487913085876</v>
       </c>
       <c r="C59">
-        <v>298.0494557106178</v>
+        <v>293.8211375304465</v>
       </c>
       <c r="D59">
-        <v>490.2234557106178</v>
+        <v>490.5771375304467</v>
       </c>
       <c r="E59">
-        <v>116.074</v>
+        <v>120.6560000000001</v>
       </c>
       <c r="F59">
-        <v>261.174</v>
+        <v>265.7560000000001</v>
       </c>
       <c r="G59">
         <v>69</v>
@@ -6107,28 +6107,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M59">
-        <v>18.7784106</v>
+        <v>19.10785640000001</v>
       </c>
       <c r="N59">
-        <v>31.08825606666667</v>
+        <v>30.75881026666667</v>
       </c>
       <c r="O59">
-        <v>6.994857615000001</v>
+        <v>6.92073231</v>
       </c>
       <c r="P59">
-        <v>24.09339845166667</v>
+        <v>23.83807795666667</v>
       </c>
       <c r="Q59">
-        <v>30.89339845166667</v>
+        <v>30.63807795666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1749560078252972</v>
+        <v>0.1776898602585419</v>
       </c>
       <c r="T59">
-        <v>0.9005328451751425</v>
+        <v>0.9195944742193677</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.655531808781871</v>
+        <v>2.609746777595976</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1069487913085876</v>
+        <v>0.1069046742522974</v>
       </c>
       <c r="C60">
-        <v>293.8211375304466</v>
+        <v>289.5933300608207</v>
       </c>
       <c r="D60">
-        <v>490.5771375304466</v>
+        <v>490.9313300608208</v>
       </c>
       <c r="E60">
-        <v>120.656</v>
+        <v>125.238</v>
       </c>
       <c r="F60">
-        <v>265.756</v>
+        <v>270.338</v>
       </c>
       <c r="G60">
         <v>69</v>
@@ -6189,28 +6189,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M60">
-        <v>19.1078564</v>
+        <v>19.4373022</v>
       </c>
       <c r="N60">
-        <v>30.75881026666667</v>
+        <v>30.42936446666667</v>
       </c>
       <c r="O60">
-        <v>6.920732310000001</v>
+        <v>6.846607005000001</v>
       </c>
       <c r="P60">
-        <v>23.83807795666667</v>
+        <v>23.58275746166667</v>
       </c>
       <c r="Q60">
-        <v>30.63807795666667</v>
+        <v>30.38275746166667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1776898602585419</v>
+        <v>0.1805570713470668</v>
       </c>
       <c r="T60">
-        <v>0.9195944742193675</v>
+        <v>0.9395859388267256</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.609746777595977</v>
+        <v>2.565513781365536</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1069046742522974</v>
+        <v>0.1068605571960072</v>
       </c>
       <c r="C61">
-        <v>289.5933300608207</v>
+        <v>285.3660344087257</v>
       </c>
       <c r="D61">
-        <v>490.9313300608208</v>
+        <v>491.2860344087257</v>
       </c>
       <c r="E61">
-        <v>125.238</v>
+        <v>129.82</v>
       </c>
       <c r="F61">
-        <v>270.338</v>
+        <v>274.92</v>
       </c>
       <c r="G61">
         <v>69</v>
@@ -6271,28 +6271,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M61">
-        <v>19.4373022</v>
+        <v>19.766748</v>
       </c>
       <c r="N61">
-        <v>30.42936446666667</v>
+        <v>30.09991866666667</v>
       </c>
       <c r="O61">
-        <v>6.846607005000001</v>
+        <v>6.772481700000001</v>
       </c>
       <c r="P61">
-        <v>23.58275746166667</v>
+        <v>23.32743696666667</v>
       </c>
       <c r="Q61">
-        <v>30.38275746166667</v>
+        <v>30.12743696666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1805570713470668</v>
+        <v>0.183567642990018</v>
       </c>
       <c r="T61">
-        <v>0.9395859388267256</v>
+        <v>0.9605769766644513</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.565513781365536</v>
+        <v>2.522755218342778</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1068605571960072</v>
+        <v>0.108660165139717</v>
       </c>
       <c r="C62">
-        <v>285.3660344087257</v>
+        <v>266.7191294217513</v>
       </c>
       <c r="D62">
-        <v>491.2860344087257</v>
+        <v>477.2211294217514</v>
       </c>
       <c r="E62">
-        <v>129.82</v>
+        <v>134.402</v>
       </c>
       <c r="F62">
-        <v>274.92</v>
+        <v>279.502</v>
       </c>
       <c r="G62">
         <v>69</v>
@@ -6353,45 +6353,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M62">
-        <v>19.766748</v>
+        <v>21.1862516</v>
       </c>
       <c r="N62">
-        <v>30.09991866666667</v>
+        <v>28.68041506666667</v>
       </c>
       <c r="O62">
-        <v>6.772481700000001</v>
+        <v>6.453093390000001</v>
       </c>
       <c r="P62">
-        <v>23.32743696666667</v>
+        <v>22.22732167666667</v>
       </c>
       <c r="Q62">
-        <v>30.12743696666667</v>
+        <v>29.02732167666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.183567642990018</v>
+        <v>0.1867326029223513</v>
       </c>
       <c r="T62">
-        <v>0.9605769766644513</v>
+        <v>0.9826444779810353</v>
       </c>
       <c r="U62">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.225</v>
       </c>
       <c r="W62">
-        <v>0.05572250000000001</v>
+        <v>0.05874500000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.522755218342778</v>
+        <v>2.353727672462205</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.108660165139717</v>
+        <v>0.1086462730834268</v>
       </c>
       <c r="C63">
-        <v>266.7191294217513</v>
+        <v>262.2426182990949</v>
       </c>
       <c r="D63">
-        <v>477.2211294217514</v>
+        <v>477.3266182990948</v>
       </c>
       <c r="E63">
-        <v>134.402</v>
+        <v>138.984</v>
       </c>
       <c r="F63">
-        <v>279.502</v>
+        <v>284.084</v>
       </c>
       <c r="G63">
         <v>69</v>
@@ -6435,28 +6435,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M63">
-        <v>21.1862516</v>
+        <v>21.5335672</v>
       </c>
       <c r="N63">
-        <v>28.68041506666667</v>
+        <v>28.33309946666667</v>
       </c>
       <c r="O63">
-        <v>6.453093390000001</v>
+        <v>6.374947380000001</v>
       </c>
       <c r="P63">
-        <v>22.22732167666667</v>
+        <v>21.95815208666667</v>
       </c>
       <c r="Q63">
-        <v>29.02732167666667</v>
+        <v>28.75815208666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1867326029223513</v>
+        <v>0.1900641396932285</v>
       </c>
       <c r="T63">
-        <v>0.9826444779810353</v>
+        <v>1.005873426735334</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.353727672462205</v>
+        <v>2.315764322906363</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1086462730834268</v>
+        <v>0.1086323810271366</v>
       </c>
       <c r="C64">
-        <v>262.2426182990949</v>
+        <v>257.766153823005</v>
       </c>
       <c r="D64">
-        <v>477.3266182990948</v>
+        <v>477.432153823005</v>
       </c>
       <c r="E64">
-        <v>138.984</v>
+        <v>143.5660000000001</v>
       </c>
       <c r="F64">
-        <v>284.084</v>
+        <v>288.6660000000001</v>
       </c>
       <c r="G64">
         <v>69</v>
@@ -6517,28 +6517,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M64">
-        <v>21.5335672</v>
+        <v>21.88088280000001</v>
       </c>
       <c r="N64">
-        <v>28.33309946666667</v>
+        <v>27.98578386666667</v>
       </c>
       <c r="O64">
-        <v>6.374947380000001</v>
+        <v>6.296801370000001</v>
       </c>
       <c r="P64">
-        <v>21.95815208666667</v>
+        <v>21.68898249666667</v>
       </c>
       <c r="Q64">
-        <v>28.75815208666667</v>
+        <v>28.48898249666667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1900641396932285</v>
+        <v>0.1935757595328017</v>
       </c>
       <c r="T64">
-        <v>1.005873426735334</v>
+        <v>1.030357994341216</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.315764322906363</v>
+        <v>2.279006159050706</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1086323810271366</v>
+        <v>0.1086184889708464</v>
       </c>
       <c r="C65">
-        <v>257.766153823005</v>
+        <v>253.2897360244287</v>
       </c>
       <c r="D65">
-        <v>477.432153823005</v>
+        <v>477.5377360244288</v>
       </c>
       <c r="E65">
-        <v>143.5660000000001</v>
+        <v>148.1480000000001</v>
       </c>
       <c r="F65">
-        <v>288.6660000000001</v>
+        <v>293.248</v>
       </c>
       <c r="G65">
         <v>69</v>
@@ -6599,28 +6599,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M65">
-        <v>21.88088280000001</v>
+        <v>22.2281984</v>
       </c>
       <c r="N65">
-        <v>27.98578386666667</v>
+        <v>27.63846826666667</v>
       </c>
       <c r="O65">
-        <v>6.296801370000001</v>
+        <v>6.218655360000001</v>
       </c>
       <c r="P65">
-        <v>21.68898249666667</v>
+        <v>21.41981290666667</v>
       </c>
       <c r="Q65">
-        <v>28.48898249666667</v>
+        <v>28.21981290666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1935757595328017</v>
+        <v>0.1972824693634623</v>
       </c>
       <c r="T65">
-        <v>1.030357994341216</v>
+        <v>1.056202815702981</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.279006159050706</v>
+        <v>2.243396687815539</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1086184889708464</v>
+        <v>0.1086045969145562</v>
       </c>
       <c r="C66">
-        <v>253.2897360244287</v>
+        <v>248.8133649343407</v>
       </c>
       <c r="D66">
-        <v>477.5377360244288</v>
+        <v>477.6433649343407</v>
       </c>
       <c r="E66">
-        <v>148.1480000000001</v>
+        <v>152.73</v>
       </c>
       <c r="F66">
-        <v>293.248</v>
+        <v>297.83</v>
       </c>
       <c r="G66">
         <v>69</v>
@@ -6681,28 +6681,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M66">
-        <v>22.2281984</v>
+        <v>22.57551400000001</v>
       </c>
       <c r="N66">
-        <v>27.63846826666667</v>
+        <v>27.29115266666667</v>
       </c>
       <c r="O66">
-        <v>6.218655360000001</v>
+        <v>6.14050935</v>
       </c>
       <c r="P66">
-        <v>21.41981290666667</v>
+        <v>21.15064331666667</v>
       </c>
       <c r="Q66">
-        <v>28.21981290666667</v>
+        <v>27.95064331666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1972824693634623</v>
+        <v>0.2012009911844464</v>
       </c>
       <c r="T66">
-        <v>1.056202815702981</v>
+        <v>1.083524483999703</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.243396687815539</v>
+        <v>2.208882892618377</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1086045969145562</v>
+        <v>0.1085907048582661</v>
       </c>
       <c r="C67">
-        <v>248.8133649343407</v>
+        <v>244.3370405837427</v>
       </c>
       <c r="D67">
-        <v>477.6433649343407</v>
+        <v>477.7490405837428</v>
       </c>
       <c r="E67">
-        <v>152.73</v>
+        <v>157.312</v>
       </c>
       <c r="F67">
-        <v>297.83</v>
+        <v>302.412</v>
       </c>
       <c r="G67">
         <v>69</v>
@@ -6763,28 +6763,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M67">
-        <v>22.57551400000001</v>
+        <v>22.9228296</v>
       </c>
       <c r="N67">
-        <v>27.29115266666667</v>
+        <v>26.94383706666667</v>
       </c>
       <c r="O67">
-        <v>6.14050935</v>
+        <v>6.062363340000001</v>
       </c>
       <c r="P67">
-        <v>21.15064331666667</v>
+        <v>20.88147372666667</v>
       </c>
       <c r="Q67">
-        <v>27.95064331666667</v>
+        <v>27.68147372666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2012009911844464</v>
+        <v>0.2053500142890178</v>
       </c>
       <c r="T67">
-        <v>1.083524483999703</v>
+        <v>1.112453309255057</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.208882892618377</v>
+        <v>2.175414970002947</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1085907048582661</v>
+        <v>0.1085768128019759</v>
       </c>
       <c r="C68">
-        <v>244.3370405837427</v>
+        <v>239.8607630036639</v>
       </c>
       <c r="D68">
-        <v>477.7490405837428</v>
+        <v>477.854763003664</v>
       </c>
       <c r="E68">
-        <v>157.312</v>
+        <v>161.894</v>
       </c>
       <c r="F68">
-        <v>302.412</v>
+        <v>306.994</v>
       </c>
       <c r="G68">
         <v>69</v>
@@ -6845,28 +6845,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M68">
-        <v>22.9228296</v>
+        <v>23.27014520000001</v>
       </c>
       <c r="N68">
-        <v>26.94383706666667</v>
+        <v>26.59652146666667</v>
       </c>
       <c r="O68">
-        <v>6.062363340000001</v>
+        <v>5.984217330000001</v>
       </c>
       <c r="P68">
-        <v>20.88147372666667</v>
+        <v>20.61230413666667</v>
       </c>
       <c r="Q68">
-        <v>27.68147372666667</v>
+        <v>27.41230413666667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2053500142890178</v>
+        <v>0.2097504933393208</v>
       </c>
       <c r="T68">
-        <v>1.112453309255057</v>
+        <v>1.143135396647099</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.175414970002947</v>
+        <v>2.142946089853649</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1085768128019759</v>
+        <v>0.1085629207456857</v>
       </c>
       <c r="C69">
-        <v>239.8607630036639</v>
+        <v>235.3845322251614</v>
       </c>
       <c r="D69">
-        <v>477.854763003664</v>
+        <v>477.9605322251615</v>
       </c>
       <c r="E69">
-        <v>161.894</v>
+        <v>166.4760000000001</v>
       </c>
       <c r="F69">
-        <v>306.994</v>
+        <v>311.5760000000001</v>
       </c>
       <c r="G69">
         <v>69</v>
@@ -6927,28 +6927,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M69">
-        <v>23.27014520000001</v>
+        <v>23.61746080000001</v>
       </c>
       <c r="N69">
-        <v>26.59652146666667</v>
+        <v>26.24920586666667</v>
       </c>
       <c r="O69">
-        <v>5.984217330000001</v>
+        <v>5.906071320000001</v>
       </c>
       <c r="P69">
-        <v>20.61230413666667</v>
+        <v>20.34313454666667</v>
       </c>
       <c r="Q69">
-        <v>27.41230413666667</v>
+        <v>27.14313454666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2097504933393208</v>
+        <v>0.2144260023302678</v>
       </c>
       <c r="T69">
-        <v>1.143135396647099</v>
+        <v>1.175735114501143</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.142946089853649</v>
+        <v>2.111432176767566</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1085629207456857</v>
+        <v>0.1085490286893955</v>
       </c>
       <c r="C70">
-        <v>235.3845322251614</v>
+        <v>230.9083482793197</v>
       </c>
       <c r="D70">
-        <v>477.9605322251615</v>
+        <v>478.0663482793197</v>
       </c>
       <c r="E70">
-        <v>166.4760000000001</v>
+        <v>171.0580000000001</v>
       </c>
       <c r="F70">
-        <v>311.5760000000001</v>
+        <v>316.1580000000001</v>
       </c>
       <c r="G70">
         <v>69</v>
@@ -7009,28 +7009,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M70">
-        <v>23.61746080000001</v>
+        <v>23.96477640000001</v>
       </c>
       <c r="N70">
-        <v>26.24920586666667</v>
+        <v>25.90189026666667</v>
       </c>
       <c r="O70">
-        <v>5.906071320000001</v>
+        <v>5.827925309999999</v>
       </c>
       <c r="P70">
-        <v>20.34313454666667</v>
+        <v>20.07396495666666</v>
       </c>
       <c r="Q70">
-        <v>27.14313454666667</v>
+        <v>26.87396495666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2144260023302678</v>
+        <v>0.2194031570625661</v>
       </c>
       <c r="T70">
-        <v>1.175735114501143</v>
+        <v>1.210438039958673</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.111432176767566</v>
+        <v>2.080831710437601</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1085490286893955</v>
+        <v>0.1085351366331053</v>
       </c>
       <c r="C71">
-        <v>230.9083482793197</v>
+        <v>226.4322111972501</v>
       </c>
       <c r="D71">
-        <v>478.0663482793197</v>
+        <v>478.1722111972501</v>
       </c>
       <c r="E71">
-        <v>171.0580000000001</v>
+        <v>175.6400000000001</v>
       </c>
       <c r="F71">
-        <v>316.1580000000001</v>
+        <v>320.7400000000001</v>
       </c>
       <c r="G71">
         <v>69</v>
@@ -7091,28 +7091,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M71">
-        <v>23.96477640000001</v>
+        <v>24.31209200000001</v>
       </c>
       <c r="N71">
-        <v>25.90189026666667</v>
+        <v>25.55457466666667</v>
       </c>
       <c r="O71">
-        <v>5.827925309999999</v>
+        <v>5.7497793</v>
       </c>
       <c r="P71">
-        <v>20.07396495666666</v>
+        <v>19.80479536666667</v>
       </c>
       <c r="Q71">
-        <v>26.87396495666666</v>
+        <v>26.60479536666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2194031570625661</v>
+        <v>0.224712122110351</v>
       </c>
       <c r="T71">
-        <v>1.210438039958673</v>
+        <v>1.247454493780039</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.080831710437601</v>
+        <v>2.051105543145636</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1085351366331053</v>
+        <v>0.1085212445768151</v>
       </c>
       <c r="C72">
-        <v>226.4322111972501</v>
+        <v>221.9561210100922</v>
       </c>
       <c r="D72">
-        <v>478.1722111972501</v>
+        <v>478.2781210100923</v>
       </c>
       <c r="E72">
-        <v>175.6400000000001</v>
+        <v>180.2220000000001</v>
       </c>
       <c r="F72">
-        <v>320.7400000000001</v>
+        <v>325.3220000000001</v>
       </c>
       <c r="G72">
         <v>69</v>
@@ -7173,28 +7173,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M72">
-        <v>24.31209200000001</v>
+        <v>24.65940760000001</v>
       </c>
       <c r="N72">
-        <v>25.55457466666667</v>
+        <v>25.20725906666667</v>
       </c>
       <c r="O72">
-        <v>5.7497793</v>
+        <v>5.671633290000001</v>
       </c>
       <c r="P72">
-        <v>19.80479536666667</v>
+        <v>19.53562577666667</v>
       </c>
       <c r="Q72">
-        <v>26.60479536666667</v>
+        <v>26.33562577666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.224712122110351</v>
+        <v>0.2303872226786728</v>
       </c>
       <c r="T72">
-        <v>1.247454493780039</v>
+        <v>1.287023806485638</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.051105543145636</v>
+        <v>2.022216732678796</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1085212445768151</v>
+        <v>0.1164309525205249</v>
       </c>
       <c r="C73">
-        <v>221.956121010092</v>
+        <v>163.8134635638147</v>
       </c>
       <c r="D73">
-        <v>478.2781210100921</v>
+        <v>424.7174635638146</v>
       </c>
       <c r="E73">
-        <v>180.222</v>
+        <v>184.804</v>
       </c>
       <c r="F73">
-        <v>325.322</v>
+        <v>329.904</v>
       </c>
       <c r="G73">
         <v>69</v>
@@ -7255,45 +7255,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M73">
-        <v>24.6594076</v>
+        <v>29.69136</v>
       </c>
       <c r="N73">
-        <v>25.20725906666667</v>
+        <v>20.17530666666667</v>
       </c>
       <c r="O73">
-        <v>5.671633290000002</v>
+        <v>4.539444000000002</v>
       </c>
       <c r="P73">
-        <v>19.53562577666667</v>
+        <v>15.63586266666667</v>
       </c>
       <c r="Q73">
-        <v>26.33562577666667</v>
+        <v>22.43586266666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2303872226786727</v>
+        <v>0.2364676875733032</v>
       </c>
       <c r="T73">
-        <v>1.287023806485637</v>
+        <v>1.329419498670207</v>
       </c>
       <c r="U73">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V73">
         <v>0.225</v>
       </c>
       <c r="W73">
-        <v>0.05874500000000001</v>
+        <v>0.06974999999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.022216732678796</v>
+        <v>1.67950092776709</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1164309525205249</v>
+        <v>0.1165271104642347</v>
       </c>
       <c r="C74">
-        <v>163.8134635638147</v>
+        <v>158.6540335276393</v>
       </c>
       <c r="D74">
-        <v>424.7174635638146</v>
+        <v>424.1400335276394</v>
       </c>
       <c r="E74">
-        <v>184.804</v>
+        <v>189.3860000000001</v>
       </c>
       <c r="F74">
-        <v>329.904</v>
+        <v>334.486</v>
       </c>
       <c r="G74">
         <v>69</v>
@@ -7337,28 +7337,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M74">
-        <v>29.69136</v>
+        <v>30.10374</v>
       </c>
       <c r="N74">
-        <v>20.17530666666667</v>
+        <v>19.76292666666667</v>
       </c>
       <c r="O74">
-        <v>4.539444000000002</v>
+        <v>4.446658500000002</v>
       </c>
       <c r="P74">
-        <v>15.63586266666667</v>
+        <v>15.31626816666667</v>
       </c>
       <c r="Q74">
-        <v>22.43586266666667</v>
+        <v>22.11626816666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2364676875733032</v>
+        <v>0.2429985572749433</v>
       </c>
       <c r="T74">
-        <v>1.329419498670207</v>
+        <v>1.374955612498078</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.67950092776709</v>
+        <v>1.656494065742883</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1165271104642347</v>
+        <v>0.1166232684079445</v>
       </c>
       <c r="C75">
-        <v>158.6540335276393</v>
+        <v>153.4961714644244</v>
       </c>
       <c r="D75">
-        <v>424.1400335276394</v>
+        <v>423.5641714644244</v>
       </c>
       <c r="E75">
-        <v>189.3860000000001</v>
+        <v>193.968</v>
       </c>
       <c r="F75">
-        <v>334.486</v>
+        <v>339.068</v>
       </c>
       <c r="G75">
         <v>69</v>
@@ -7419,28 +7419,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M75">
-        <v>30.10374</v>
+        <v>30.51612</v>
       </c>
       <c r="N75">
-        <v>19.76292666666667</v>
+        <v>19.35054666666667</v>
       </c>
       <c r="O75">
-        <v>4.446658500000002</v>
+        <v>4.353873000000002</v>
       </c>
       <c r="P75">
-        <v>15.31626816666667</v>
+        <v>14.99667366666667</v>
       </c>
       <c r="Q75">
-        <v>22.11626816666667</v>
+        <v>21.79667366666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2429985572749433</v>
+        <v>0.2500318015690173</v>
       </c>
       <c r="T75">
-        <v>1.374955612498078</v>
+        <v>1.423994504312708</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.656494065742883</v>
+        <v>1.634109010800412</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1166232684079445</v>
+        <v>0.1167194263516543</v>
       </c>
       <c r="C76">
-        <v>153.4961714644244</v>
+        <v>148.3398709962394</v>
       </c>
       <c r="D76">
-        <v>423.5641714644244</v>
+        <v>422.9898709962394</v>
       </c>
       <c r="E76">
-        <v>193.968</v>
+        <v>198.55</v>
       </c>
       <c r="F76">
-        <v>339.068</v>
+        <v>343.65</v>
       </c>
       <c r="G76">
         <v>69</v>
@@ -7501,28 +7501,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M76">
-        <v>30.51612</v>
+        <v>30.9285</v>
       </c>
       <c r="N76">
-        <v>19.35054666666667</v>
+        <v>18.93816666666667</v>
       </c>
       <c r="O76">
-        <v>4.353873000000002</v>
+        <v>4.261087500000001</v>
       </c>
       <c r="P76">
-        <v>14.99667366666667</v>
+        <v>14.67707916666667</v>
       </c>
       <c r="Q76">
-        <v>21.79667366666667</v>
+        <v>21.47707916666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2500318015690173</v>
+        <v>0.2576277054066173</v>
       </c>
       <c r="T76">
-        <v>1.423994504312708</v>
+        <v>1.476956507472509</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.634109010800412</v>
+        <v>1.612320890656406</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1167194263516543</v>
+        <v>0.1168155842953641</v>
       </c>
       <c r="C77">
-        <v>148.3398709962394</v>
+        <v>143.1851257796978</v>
       </c>
       <c r="D77">
-        <v>422.9898709962394</v>
+        <v>422.4171257796978</v>
       </c>
       <c r="E77">
-        <v>198.55</v>
+        <v>203.132</v>
       </c>
       <c r="F77">
-        <v>343.65</v>
+        <v>348.232</v>
       </c>
       <c r="G77">
         <v>69</v>
@@ -7583,28 +7583,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M77">
-        <v>30.9285</v>
+        <v>31.34088</v>
       </c>
       <c r="N77">
-        <v>18.93816666666667</v>
+        <v>18.52578666666667</v>
       </c>
       <c r="O77">
-        <v>4.261087500000001</v>
+        <v>4.168302000000002</v>
       </c>
       <c r="P77">
-        <v>14.67707916666667</v>
+        <v>14.35748466666667</v>
       </c>
       <c r="Q77">
-        <v>21.47707916666667</v>
+        <v>21.15748466666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2576277054066173</v>
+        <v>0.2658566012306839</v>
       </c>
       <c r="T77">
-        <v>1.476956507472509</v>
+        <v>1.534332010895627</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.612320890656406</v>
+        <v>1.591106142095138</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1168155842953641</v>
+        <v>0.1169117422390739</v>
       </c>
       <c r="C78">
-        <v>143.1851257796978</v>
+        <v>138.0319295057234</v>
       </c>
       <c r="D78">
-        <v>422.4171257796978</v>
+        <v>421.8459295057234</v>
       </c>
       <c r="E78">
-        <v>203.132</v>
+        <v>207.714</v>
       </c>
       <c r="F78">
-        <v>348.232</v>
+        <v>352.814</v>
       </c>
       <c r="G78">
         <v>69</v>
@@ -7665,28 +7665,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M78">
-        <v>31.34088</v>
+        <v>31.75326</v>
       </c>
       <c r="N78">
-        <v>18.52578666666667</v>
+        <v>18.11340666666667</v>
       </c>
       <c r="O78">
-        <v>4.168302000000002</v>
+        <v>4.075516500000002</v>
       </c>
       <c r="P78">
-        <v>14.35748466666667</v>
+        <v>14.03789016666667</v>
       </c>
       <c r="Q78">
-        <v>21.15748466666667</v>
+        <v>20.83789016666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2658566012306839</v>
+        <v>0.274801053213365</v>
       </c>
       <c r="T78">
-        <v>1.534332010895627</v>
+        <v>1.59669668852945</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.591106142095138</v>
+        <v>1.570442425964032</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1169117422390739</v>
+        <v>0.1170079001827837</v>
       </c>
       <c r="C79">
-        <v>138.0319295057234</v>
+        <v>132.8802758993189</v>
       </c>
       <c r="D79">
-        <v>421.8459295057234</v>
+        <v>421.2762758993189</v>
       </c>
       <c r="E79">
-        <v>207.714</v>
+        <v>212.2960000000001</v>
       </c>
       <c r="F79">
-        <v>352.814</v>
+        <v>357.3960000000001</v>
       </c>
       <c r="G79">
         <v>69</v>
@@ -7747,28 +7747,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M79">
-        <v>31.75326</v>
+        <v>32.16564</v>
       </c>
       <c r="N79">
-        <v>18.11340666666667</v>
+        <v>17.70102666666667</v>
       </c>
       <c r="O79">
-        <v>4.075516500000002</v>
+        <v>3.982731000000001</v>
       </c>
       <c r="P79">
-        <v>14.03789016666667</v>
+        <v>13.71829566666667</v>
       </c>
       <c r="Q79">
-        <v>20.83789016666667</v>
+        <v>20.51829566666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.274801053213365</v>
+        <v>0.2845586371944716</v>
       </c>
       <c r="T79">
-        <v>1.59669668852945</v>
+        <v>1.664730882311803</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.570442425964032</v>
+        <v>1.550308548708083</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1170079001827837</v>
+        <v>0.1171040581264935</v>
       </c>
       <c r="C80">
-        <v>132.8802758993189</v>
+        <v>127.7301587193352</v>
       </c>
       <c r="D80">
-        <v>421.2762758993189</v>
+        <v>420.7081587193353</v>
       </c>
       <c r="E80">
-        <v>212.2960000000001</v>
+        <v>216.8780000000001</v>
       </c>
       <c r="F80">
-        <v>357.3960000000001</v>
+        <v>361.9780000000001</v>
       </c>
       <c r="G80">
         <v>69</v>
@@ -7829,28 +7829,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M80">
-        <v>32.16564</v>
+        <v>32.57802</v>
       </c>
       <c r="N80">
-        <v>17.70102666666667</v>
+        <v>17.28864666666667</v>
       </c>
       <c r="O80">
-        <v>3.982731000000001</v>
+        <v>3.889945500000001</v>
       </c>
       <c r="P80">
-        <v>13.71829566666667</v>
+        <v>13.39870116666667</v>
       </c>
       <c r="Q80">
-        <v>20.51829566666667</v>
+        <v>20.19870116666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2845586371944716</v>
+        <v>0.2952455148880646</v>
       </c>
       <c r="T80">
-        <v>1.664730882311803</v>
+        <v>1.739244523121047</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.550308548708083</v>
+        <v>1.530684389863677</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1171040581264935</v>
+        <v>0.1172002160702034</v>
       </c>
       <c r="C81">
-        <v>127.7301587193352</v>
+        <v>122.5815717582451</v>
       </c>
       <c r="D81">
-        <v>420.7081587193353</v>
+        <v>420.1415717582452</v>
       </c>
       <c r="E81">
-        <v>216.8780000000001</v>
+        <v>221.4600000000001</v>
       </c>
       <c r="F81">
-        <v>361.9780000000001</v>
+        <v>366.5600000000001</v>
       </c>
       <c r="G81">
         <v>69</v>
@@ -7911,28 +7911,28 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M81">
-        <v>32.57802</v>
+        <v>32.9904</v>
       </c>
       <c r="N81">
-        <v>17.28864666666667</v>
+        <v>16.87626666666667</v>
       </c>
       <c r="O81">
-        <v>3.889945500000001</v>
+        <v>3.797160000000002</v>
       </c>
       <c r="P81">
-        <v>13.39870116666667</v>
+        <v>13.07910666666667</v>
       </c>
       <c r="Q81">
-        <v>20.19870116666667</v>
+        <v>19.87910666666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2952455148880646</v>
+        <v>0.3070010803510169</v>
       </c>
       <c r="T81">
-        <v>1.739244523121047</v>
+        <v>1.821209528011215</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.530684389863677</v>
+        <v>1.511550834990381</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1172002160702034</v>
+        <v>0.1562036491780617</v>
       </c>
       <c r="C82">
-        <v>122.5815717582451</v>
+        <v>-30.4281642079265</v>
       </c>
       <c r="D82">
-        <v>420.1415717582452</v>
+        <v>271.7138357920736</v>
       </c>
       <c r="E82">
-        <v>221.4600000000001</v>
+        <v>226.0420000000001</v>
       </c>
       <c r="F82">
-        <v>366.5600000000001</v>
+        <v>371.1420000000001</v>
       </c>
       <c r="G82">
         <v>69</v>
@@ -7993,45 +7993,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M82">
-        <v>32.9904</v>
+        <v>54.48364560000001</v>
       </c>
       <c r="N82">
-        <v>16.87626666666667</v>
+        <v>-4.616978933333336</v>
       </c>
       <c r="O82">
-        <v>3.797160000000002</v>
+        <v>-1.03882026</v>
       </c>
       <c r="P82">
-        <v>13.07910666666667</v>
+        <v>-3.578158673333335</v>
       </c>
       <c r="Q82">
-        <v>19.87910666666667</v>
+        <v>3.221841326666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3070010803510169</v>
+        <v>0.3251724879205575</v>
       </c>
       <c r="T82">
-        <v>1.821209528011215</v>
+        <v>1.947908623430533</v>
       </c>
       <c r="U82">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.225</v>
+        <v>0.2059333562657195</v>
       </c>
       <c r="W82">
-        <v>0.06974999999999999</v>
+        <v>0.1165689833001924</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.511550834990381</v>
+        <v>0.9152593611809755</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1562036491780617</v>
+        <v>0.1572136491780617</v>
       </c>
       <c r="C83">
-        <v>-30.4281642079265</v>
+        <v>-37.47333614578667</v>
       </c>
       <c r="D83">
-        <v>271.7138357920736</v>
+        <v>269.2506638542134</v>
       </c>
       <c r="E83">
-        <v>226.0420000000001</v>
+        <v>230.6240000000001</v>
       </c>
       <c r="F83">
-        <v>371.1420000000001</v>
+        <v>375.724</v>
       </c>
       <c r="G83">
         <v>69</v>
@@ -8075,37 +8075,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M83">
-        <v>54.48364560000001</v>
+        <v>55.15628320000001</v>
       </c>
       <c r="N83">
-        <v>-4.616978933333336</v>
+        <v>-5.289616533333337</v>
       </c>
       <c r="O83">
-        <v>-1.03882026</v>
+        <v>-1.190163720000001</v>
       </c>
       <c r="P83">
-        <v>-3.578158673333335</v>
+        <v>-4.099452813333336</v>
       </c>
       <c r="Q83">
-        <v>3.221841326666666</v>
+        <v>2.700547186666665</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3251724879205575</v>
+        <v>0.3406931816939218</v>
       </c>
       <c r="T83">
-        <v>1.947908623430533</v>
+        <v>2.056125769176674</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2059333562657195</v>
+        <v>0.2034219738722351</v>
       </c>
       <c r="W83">
-        <v>0.1165689833001924</v>
+        <v>0.1169376542355559</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9152593611809755</v>
+        <v>0.9040976616543782</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1572136491780617</v>
+        <v>0.1582236491780618</v>
       </c>
       <c r="C84">
-        <v>-37.47333614578667</v>
+        <v>-44.47425042655374</v>
       </c>
       <c r="D84">
-        <v>269.2506638542134</v>
+        <v>266.8317495734464</v>
       </c>
       <c r="E84">
-        <v>230.6240000000001</v>
+        <v>235.2060000000001</v>
       </c>
       <c r="F84">
-        <v>375.724</v>
+        <v>380.3060000000001</v>
       </c>
       <c r="G84">
         <v>69</v>
@@ -8157,37 +8157,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M84">
-        <v>55.15628320000001</v>
+        <v>55.82892080000002</v>
       </c>
       <c r="N84">
-        <v>-5.289616533333337</v>
+        <v>-5.962254133333346</v>
       </c>
       <c r="O84">
-        <v>-1.190163720000001</v>
+        <v>-1.341507180000003</v>
       </c>
       <c r="P84">
-        <v>-4.099452813333336</v>
+        <v>-4.620746953333343</v>
       </c>
       <c r="Q84">
-        <v>2.700547186666665</v>
+        <v>2.179253046666657</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3406931816939218</v>
+        <v>0.3580398394406231</v>
       </c>
       <c r="T84">
-        <v>2.056125769176674</v>
+        <v>2.177074343834125</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2034219738722351</v>
+        <v>0.2009711067171479</v>
       </c>
       <c r="W84">
-        <v>0.1169376542355559</v>
+        <v>0.1172974415339227</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9040976616543782</v>
+        <v>0.8932049187428796</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1582236491780618</v>
+        <v>0.1592336491780618</v>
       </c>
       <c r="C85">
-        <v>-44.47425042655374</v>
+        <v>-51.43208924529915</v>
       </c>
       <c r="D85">
-        <v>266.8317495734464</v>
+        <v>264.4559107547009</v>
       </c>
       <c r="E85">
-        <v>235.2060000000001</v>
+        <v>239.7880000000001</v>
       </c>
       <c r="F85">
-        <v>380.3060000000001</v>
+        <v>384.8880000000001</v>
       </c>
       <c r="G85">
         <v>69</v>
@@ -8239,37 +8239,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M85">
-        <v>55.82892080000002</v>
+        <v>56.50155840000002</v>
       </c>
       <c r="N85">
-        <v>-5.962254133333346</v>
+        <v>-6.634891733333347</v>
       </c>
       <c r="O85">
-        <v>-1.341507180000003</v>
+        <v>-1.492850640000003</v>
       </c>
       <c r="P85">
-        <v>-4.620746953333343</v>
+        <v>-5.142041093333344</v>
       </c>
       <c r="Q85">
-        <v>2.179253046666657</v>
+        <v>1.657958906666656</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3580398394406231</v>
+        <v>0.3775548294056622</v>
       </c>
       <c r="T85">
-        <v>2.177074343834125</v>
+        <v>2.313141490323759</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2009711067171479</v>
+        <v>0.1985785935419437</v>
       </c>
       <c r="W85">
-        <v>0.1172974415339227</v>
+        <v>0.1176486624680427</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8932049187428796</v>
+        <v>0.8825715268530833</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1592336491780618</v>
+        <v>0.1602436491780617</v>
       </c>
       <c r="C86">
-        <v>-51.4320892452991</v>
+        <v>-58.34799306417034</v>
       </c>
       <c r="D86">
-        <v>264.4559107547009</v>
+        <v>262.1220069358297</v>
       </c>
       <c r="E86">
-        <v>239.788</v>
+        <v>244.37</v>
       </c>
       <c r="F86">
-        <v>384.888</v>
+        <v>389.47</v>
       </c>
       <c r="G86">
         <v>69</v>
@@ -8321,37 +8321,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M86">
-        <v>56.50155840000001</v>
+        <v>57.17419600000001</v>
       </c>
       <c r="N86">
-        <v>-6.634891733333333</v>
+        <v>-7.307529333333335</v>
       </c>
       <c r="O86">
-        <v>-1.49285064</v>
+        <v>-1.6441941</v>
       </c>
       <c r="P86">
-        <v>-5.142041093333333</v>
+        <v>-5.663335233333335</v>
       </c>
       <c r="Q86">
-        <v>1.657958906666668</v>
+        <v>1.136664766666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3775548294056619</v>
+        <v>0.3996718180327061</v>
       </c>
       <c r="T86">
-        <v>2.313141490323757</v>
+        <v>2.467350923012008</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1985785935419438</v>
+        <v>0.1962423747943915</v>
       </c>
       <c r="W86">
-        <v>0.1176486624680427</v>
+        <v>0.1179916193801833</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8825715268530835</v>
+        <v>0.8721883324195179</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1602436491780617</v>
+        <v>0.1612536491780617</v>
       </c>
       <c r="C87">
-        <v>-58.34799306417034</v>
+        <v>-65.22306243781031</v>
       </c>
       <c r="D87">
-        <v>262.1220069358297</v>
+        <v>259.8289375621897</v>
       </c>
       <c r="E87">
-        <v>244.37</v>
+        <v>248.952</v>
       </c>
       <c r="F87">
-        <v>389.47</v>
+        <v>394.052</v>
       </c>
       <c r="G87">
         <v>69</v>
@@ -8403,37 +8403,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M87">
-        <v>57.17419600000001</v>
+        <v>57.84683360000001</v>
       </c>
       <c r="N87">
-        <v>-7.307529333333335</v>
+        <v>-7.980166933333336</v>
       </c>
       <c r="O87">
-        <v>-1.6441941</v>
+        <v>-1.795537560000001</v>
       </c>
       <c r="P87">
-        <v>-5.663335233333335</v>
+        <v>-6.184629373333336</v>
       </c>
       <c r="Q87">
-        <v>1.136664766666666</v>
+        <v>0.6153706266666648</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3996718180327061</v>
+        <v>0.4249483764636136</v>
       </c>
       <c r="T87">
-        <v>2.467350923012008</v>
+        <v>2.643590274655722</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1962423747943915</v>
+        <v>0.193960486715387</v>
       </c>
       <c r="W87">
-        <v>0.1179916193801833</v>
+        <v>0.1183266005501812</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8721883324195179</v>
+        <v>0.862046607623942</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1612536491780617</v>
+        <v>0.1622636491780617</v>
       </c>
       <c r="C88">
-        <v>-65.22306243781031</v>
+        <v>-72.05835974379272</v>
       </c>
       <c r="D88">
-        <v>259.8289375621897</v>
+        <v>257.5756402562073</v>
       </c>
       <c r="E88">
-        <v>248.952</v>
+        <v>253.534</v>
       </c>
       <c r="F88">
-        <v>394.052</v>
+        <v>398.634</v>
       </c>
       <c r="G88">
         <v>69</v>
@@ -8485,37 +8485,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M88">
-        <v>57.84683360000001</v>
+        <v>58.51947120000001</v>
       </c>
       <c r="N88">
-        <v>-7.980166933333336</v>
+        <v>-8.652804533333331</v>
       </c>
       <c r="O88">
-        <v>-1.795537560000001</v>
+        <v>-1.94688102</v>
       </c>
       <c r="P88">
-        <v>-6.184629373333336</v>
+        <v>-6.705923513333332</v>
       </c>
       <c r="Q88">
-        <v>0.6153706266666648</v>
+        <v>0.09407648666666901</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4249483764636136</v>
+        <v>0.4541136361915838</v>
       </c>
       <c r="T88">
-        <v>2.643590274655722</v>
+        <v>2.846943372706162</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.193960486715387</v>
+        <v>0.1917310558336009</v>
       </c>
       <c r="W88">
-        <v>0.1183266005501812</v>
+        <v>0.1186538810036274</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.862046607623942</v>
+        <v>0.8521380259271152</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1622636491780617</v>
+        <v>0.1632736491780618</v>
       </c>
       <c r="C89">
-        <v>-72.05835974379272</v>
+        <v>-78.85491082379241</v>
       </c>
       <c r="D89">
-        <v>257.5756402562073</v>
+        <v>255.3610891762076</v>
       </c>
       <c r="E89">
-        <v>253.534</v>
+        <v>258.1160000000001</v>
       </c>
       <c r="F89">
-        <v>398.634</v>
+        <v>403.2160000000001</v>
       </c>
       <c r="G89">
         <v>69</v>
@@ -8567,37 +8567,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M89">
-        <v>58.51947120000001</v>
+        <v>59.19210880000001</v>
       </c>
       <c r="N89">
-        <v>-8.652804533333331</v>
+        <v>-9.32544213333334</v>
       </c>
       <c r="O89">
-        <v>-1.94688102</v>
+        <v>-2.098224480000002</v>
       </c>
       <c r="P89">
-        <v>-6.705923513333332</v>
+        <v>-7.227217653333338</v>
       </c>
       <c r="Q89">
-        <v>0.09407648666666901</v>
+        <v>-0.4272176533333374</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4541136361915838</v>
+        <v>0.4881397725408826</v>
       </c>
       <c r="T89">
-        <v>2.846943372706162</v>
+        <v>3.08418865376501</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1917310558336009</v>
+        <v>0.1895522938354918</v>
       </c>
       <c r="W89">
-        <v>0.1186538810036274</v>
+        <v>0.1189737232649498</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8521380259271152</v>
+        <v>0.8424546392688523</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1632736491780618</v>
+        <v>0.1642836491780618</v>
       </c>
       <c r="C90">
-        <v>-78.85491082379241</v>
+        <v>-85.61370654081469</v>
       </c>
       <c r="D90">
-        <v>255.3610891762076</v>
+        <v>253.1842934591854</v>
       </c>
       <c r="E90">
-        <v>258.1160000000001</v>
+        <v>262.6980000000001</v>
       </c>
       <c r="F90">
-        <v>403.2160000000001</v>
+        <v>407.7980000000001</v>
       </c>
       <c r="G90">
         <v>69</v>
@@ -8649,37 +8649,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M90">
-        <v>59.19210880000001</v>
+        <v>59.86474640000002</v>
       </c>
       <c r="N90">
-        <v>-9.32544213333334</v>
+        <v>-9.998079733333341</v>
       </c>
       <c r="O90">
-        <v>-2.098224480000002</v>
+        <v>-2.249567940000002</v>
       </c>
       <c r="P90">
-        <v>-7.227217653333338</v>
+        <v>-7.748511793333339</v>
       </c>
       <c r="Q90">
-        <v>-0.4272176533333374</v>
+        <v>-0.9485117933333385</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4881397725408826</v>
+        <v>0.5283524791355083</v>
       </c>
       <c r="T90">
-        <v>3.08418865376501</v>
+        <v>3.36456944047092</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1895522938354918</v>
+        <v>0.1874224927811604</v>
       </c>
       <c r="W90">
-        <v>0.1189737232649498</v>
+        <v>0.1192863780597257</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8424546392688523</v>
+        <v>0.8329888568051573</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1642836491780618</v>
+        <v>0.1652936491780617</v>
       </c>
       <c r="C91">
-        <v>-85.61370654081469</v>
+        <v>-92.33570425745239</v>
       </c>
       <c r="D91">
-        <v>253.1842934591854</v>
+        <v>251.0442957425476</v>
       </c>
       <c r="E91">
-        <v>262.6980000000001</v>
+        <v>267.2800000000001</v>
       </c>
       <c r="F91">
-        <v>407.7980000000001</v>
+        <v>412.3800000000001</v>
       </c>
       <c r="G91">
         <v>69</v>
@@ -8731,37 +8731,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M91">
-        <v>59.86474640000002</v>
+        <v>60.53738400000001</v>
       </c>
       <c r="N91">
-        <v>-9.998079733333341</v>
+        <v>-10.67071733333334</v>
       </c>
       <c r="O91">
-        <v>-2.249567940000002</v>
+        <v>-2.4009114</v>
       </c>
       <c r="P91">
-        <v>-7.748511793333339</v>
+        <v>-8.269805933333336</v>
       </c>
       <c r="Q91">
-        <v>-0.9485117933333385</v>
+        <v>-1.469805933333335</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5283524791355083</v>
+        <v>0.576607727049059</v>
       </c>
       <c r="T91">
-        <v>3.36456944047092</v>
+        <v>3.701026384518012</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1874224927811604</v>
+        <v>0.1853400206391475</v>
       </c>
       <c r="W91">
-        <v>0.1192863780597257</v>
+        <v>0.1195920849701732</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8329888568051573</v>
+        <v>0.8237334250628779</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1652936491780617</v>
+        <v>0.1663036491780617</v>
       </c>
       <c r="C92">
-        <v>-92.33570425745239</v>
+        <v>-99.02182923980308</v>
       </c>
       <c r="D92">
-        <v>251.0442957425476</v>
+        <v>248.940170760197</v>
       </c>
       <c r="E92">
-        <v>267.2800000000001</v>
+        <v>271.8620000000001</v>
       </c>
       <c r="F92">
-        <v>412.3800000000001</v>
+        <v>416.962</v>
       </c>
       <c r="G92">
         <v>69</v>
@@ -8813,37 +8813,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M92">
-        <v>60.53738400000001</v>
+        <v>61.21002160000001</v>
       </c>
       <c r="N92">
-        <v>-10.67071733333334</v>
+        <v>-11.34335493333334</v>
       </c>
       <c r="O92">
-        <v>-2.4009114</v>
+        <v>-2.552254860000001</v>
       </c>
       <c r="P92">
-        <v>-8.269805933333336</v>
+        <v>-8.791100073333336</v>
       </c>
       <c r="Q92">
-        <v>-1.469805933333335</v>
+        <v>-1.991100073333335</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.576607727049059</v>
+        <v>0.6355863633878437</v>
       </c>
       <c r="T92">
-        <v>3.701026384518012</v>
+        <v>4.112251538353348</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1853400206391475</v>
+        <v>0.1833033171156404</v>
       </c>
       <c r="W92">
-        <v>0.1195920849701732</v>
+        <v>0.119891073047424</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8237334250628779</v>
+        <v>0.8146814094028463</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1663036491780617</v>
+        <v>0.1673136491780617</v>
       </c>
       <c r="C93">
-        <v>-99.02182923980308</v>
+        <v>-105.6729759913698</v>
       </c>
       <c r="D93">
-        <v>248.940170760197</v>
+        <v>246.8710240086303</v>
       </c>
       <c r="E93">
-        <v>271.8620000000001</v>
+        <v>276.4440000000001</v>
       </c>
       <c r="F93">
-        <v>416.962</v>
+        <v>421.544</v>
       </c>
       <c r="G93">
         <v>69</v>
@@ -8895,37 +8895,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M93">
-        <v>61.21002160000001</v>
+        <v>61.88265920000001</v>
       </c>
       <c r="N93">
-        <v>-11.34335493333334</v>
+        <v>-12.01599253333334</v>
       </c>
       <c r="O93">
-        <v>-2.552254860000001</v>
+        <v>-2.703598320000002</v>
       </c>
       <c r="P93">
-        <v>-8.791100073333336</v>
+        <v>-9.312394213333338</v>
       </c>
       <c r="Q93">
-        <v>-1.991100073333335</v>
+        <v>-2.512394213333337</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6355863633878437</v>
+        <v>0.7093096588113242</v>
       </c>
       <c r="T93">
-        <v>4.112251538353348</v>
+        <v>4.626282980647518</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1833033171156404</v>
+        <v>0.1813108897556878</v>
       </c>
       <c r="W93">
-        <v>0.119891073047424</v>
+        <v>0.120183561383865</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8146814094028463</v>
+        <v>0.8058261766919458</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1673136491780617</v>
+        <v>0.2214014560749726</v>
       </c>
       <c r="C94">
-        <v>-105.6729759913698</v>
+        <v>-186.2948481739816</v>
       </c>
       <c r="D94">
-        <v>246.8710240086303</v>
+        <v>170.8311518260185</v>
       </c>
       <c r="E94">
-        <v>276.4440000000001</v>
+        <v>281.0260000000001</v>
       </c>
       <c r="F94">
-        <v>421.544</v>
+        <v>426.1260000000001</v>
       </c>
       <c r="G94">
         <v>69</v>
@@ -8977,45 +8977,45 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M94">
-        <v>61.88265920000001</v>
+        <v>85.56610080000002</v>
       </c>
       <c r="N94">
-        <v>-12.01599253333334</v>
+        <v>-35.69943413333334</v>
       </c>
       <c r="O94">
-        <v>-2.703598320000002</v>
+        <v>-8.032372680000002</v>
       </c>
       <c r="P94">
-        <v>-9.312394213333338</v>
+        <v>-27.66706145333334</v>
       </c>
       <c r="Q94">
-        <v>-2.512394213333337</v>
+        <v>-20.86706145333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7093096588113242</v>
+        <v>0.8449225657402396</v>
       </c>
       <c r="T94">
-        <v>4.626282980647518</v>
+        <v>5.571836183905075</v>
       </c>
       <c r="U94">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1813108897556878</v>
+        <v>0.1311266949773175</v>
       </c>
       <c r="W94">
-        <v>0.120183561383865</v>
+        <v>0.1744697596485547</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.8058261766919458</v>
+        <v>0.5827853110102998</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2214014560749726</v>
+        <v>0.2229514560749725</v>
       </c>
       <c r="C95">
-        <v>-186.2948481739816</v>
+        <v>-192.3715481961946</v>
       </c>
       <c r="D95">
-        <v>170.8311518260185</v>
+        <v>169.3364518038055</v>
       </c>
       <c r="E95">
-        <v>281.0260000000001</v>
+        <v>285.6080000000001</v>
       </c>
       <c r="F95">
-        <v>426.1260000000001</v>
+        <v>430.7080000000001</v>
       </c>
       <c r="G95">
         <v>69</v>
@@ -9059,37 +9059,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M95">
-        <v>85.56610080000002</v>
+        <v>86.48616640000002</v>
       </c>
       <c r="N95">
-        <v>-35.69943413333334</v>
+        <v>-36.61949973333334</v>
       </c>
       <c r="O95">
-        <v>-8.032372680000002</v>
+        <v>-8.239387440000002</v>
       </c>
       <c r="P95">
-        <v>-27.66706145333334</v>
+        <v>-28.38011229333334</v>
       </c>
       <c r="Q95">
-        <v>-20.86706145333334</v>
+        <v>-21.58011229333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8449225657402396</v>
+        <v>0.9781096600302795</v>
       </c>
       <c r="T95">
-        <v>5.571836183905075</v>
+        <v>6.500475547889255</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1311266949773175</v>
+        <v>0.1297317301371332</v>
       </c>
       <c r="W95">
-        <v>0.1744697596485547</v>
+        <v>0.1747498685884636</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5827853110102998</v>
+        <v>0.5765854672761477</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2229514560749725</v>
+        <v>0.2245014560749726</v>
       </c>
       <c r="C96">
-        <v>-192.3715481961946</v>
+        <v>-198.4223191064092</v>
       </c>
       <c r="D96">
-        <v>169.3364518038055</v>
+        <v>167.8676808935909</v>
       </c>
       <c r="E96">
-        <v>285.6080000000001</v>
+        <v>290.1900000000001</v>
       </c>
       <c r="F96">
-        <v>430.7080000000001</v>
+        <v>435.2900000000001</v>
       </c>
       <c r="G96">
         <v>69</v>
@@ -9141,37 +9141,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M96">
-        <v>86.48616640000002</v>
+        <v>87.40623200000002</v>
       </c>
       <c r="N96">
-        <v>-36.61949973333334</v>
+        <v>-37.53956533333334</v>
       </c>
       <c r="O96">
-        <v>-8.239387440000002</v>
+        <v>-8.446402200000003</v>
       </c>
       <c r="P96">
-        <v>-28.38011229333334</v>
+        <v>-29.09316313333334</v>
       </c>
       <c r="Q96">
-        <v>-21.58011229333334</v>
+        <v>-22.29316313333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9781096600302795</v>
+        <v>1.164571592036336</v>
       </c>
       <c r="T96">
-        <v>6.500475547889255</v>
+        <v>7.800570657467111</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1297317301371332</v>
+        <v>0.128366132977795</v>
       </c>
       <c r="W96">
-        <v>0.1747498685884636</v>
+        <v>0.1750240804980588</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5765854672761477</v>
+        <v>0.5705161465679778</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2245014560749726</v>
+        <v>0.2260514560749726</v>
       </c>
       <c r="C97">
-        <v>-198.4223191064092</v>
+        <v>-204.4478298055784</v>
       </c>
       <c r="D97">
-        <v>167.8676808935909</v>
+        <v>166.4241701944217</v>
       </c>
       <c r="E97">
-        <v>290.1900000000001</v>
+        <v>294.772</v>
       </c>
       <c r="F97">
-        <v>435.2900000000001</v>
+        <v>439.8720000000001</v>
       </c>
       <c r="G97">
         <v>69</v>
@@ -9223,37 +9223,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M97">
-        <v>87.40623200000002</v>
+        <v>88.32629760000002</v>
       </c>
       <c r="N97">
-        <v>-37.53956533333334</v>
+        <v>-38.45963093333334</v>
       </c>
       <c r="O97">
-        <v>-8.446402200000003</v>
+        <v>-8.653416960000003</v>
       </c>
       <c r="P97">
-        <v>-29.09316313333334</v>
+        <v>-29.80621397333334</v>
       </c>
       <c r="Q97">
-        <v>-22.29316313333334</v>
+        <v>-23.00621397333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.164571592036336</v>
+        <v>1.444264490045421</v>
       </c>
       <c r="T97">
-        <v>7.800570657467111</v>
+        <v>9.750713321833892</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.128366132977795</v>
+        <v>0.1270289857592763</v>
       </c>
       <c r="W97">
-        <v>0.1750240804980588</v>
+        <v>0.1752925796595373</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5705161465679778</v>
+        <v>0.5645732700412279</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2260514560749726</v>
+        <v>0.2276014560749726</v>
       </c>
       <c r="C98">
-        <v>-204.4478298055784</v>
+        <v>-210.4487263830347</v>
       </c>
       <c r="D98">
-        <v>166.4241701944217</v>
+        <v>165.0052736169654</v>
       </c>
       <c r="E98">
-        <v>294.772</v>
+        <v>299.354</v>
       </c>
       <c r="F98">
-        <v>439.872</v>
+        <v>444.454</v>
       </c>
       <c r="G98">
         <v>69</v>
@@ -9305,37 +9305,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M98">
-        <v>88.3262976</v>
+        <v>89.2463632</v>
       </c>
       <c r="N98">
-        <v>-38.45963093333333</v>
+        <v>-39.37969653333333</v>
       </c>
       <c r="O98">
-        <v>-8.653416959999999</v>
+        <v>-8.860431719999999</v>
       </c>
       <c r="P98">
-        <v>-29.80621397333333</v>
+        <v>-30.51926481333333</v>
       </c>
       <c r="Q98">
-        <v>-23.00621397333333</v>
+        <v>-23.71926481333333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.444264490045417</v>
+        <v>1.910419320060556</v>
       </c>
       <c r="T98">
-        <v>9.750713321833866</v>
+        <v>13.00095109577849</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1270289857592763</v>
+        <v>0.1257194085865003</v>
       </c>
       <c r="W98">
-        <v>0.1752925796595373</v>
+        <v>0.1755555427558307</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.564573270041228</v>
+        <v>0.5587529270511122</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2276014560749726</v>
+        <v>0.2291514560749726</v>
       </c>
       <c r="C99">
-        <v>-210.4487263830347</v>
+        <v>-216.4256330807034</v>
       </c>
       <c r="D99">
-        <v>165.0052736169654</v>
+        <v>163.6103669192966</v>
       </c>
       <c r="E99">
-        <v>299.354</v>
+        <v>303.936</v>
       </c>
       <c r="F99">
-        <v>444.454</v>
+        <v>449.0360000000001</v>
       </c>
       <c r="G99">
         <v>69</v>
@@ -9387,37 +9387,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M99">
-        <v>89.2463632</v>
+        <v>90.16642880000002</v>
       </c>
       <c r="N99">
-        <v>-39.37969653333333</v>
+        <v>-40.29976213333335</v>
       </c>
       <c r="O99">
-        <v>-8.860431719999999</v>
+        <v>-9.067446480000003</v>
       </c>
       <c r="P99">
-        <v>-30.51926481333333</v>
+        <v>-31.23231565333334</v>
       </c>
       <c r="Q99">
-        <v>-23.71926481333333</v>
+        <v>-24.43231565333334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.910419320060556</v>
+        <v>2.842728980090834</v>
       </c>
       <c r="T99">
-        <v>13.00095109577849</v>
+        <v>19.50142664366773</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1257194085865003</v>
+        <v>0.1244365574784747</v>
       </c>
       <c r="W99">
-        <v>0.1755555427558307</v>
+        <v>0.1758131392583223</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5587529270511122</v>
+        <v>0.5530513665709988</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2291514560749726</v>
+        <v>0.2307014560749726</v>
       </c>
       <c r="C100">
-        <v>-216.4256330807034</v>
+        <v>-222.3791532088201</v>
       </c>
       <c r="D100">
-        <v>163.6103669192966</v>
+        <v>162.2388467911799</v>
       </c>
       <c r="E100">
-        <v>303.936</v>
+        <v>308.518</v>
       </c>
       <c r="F100">
-        <v>449.0360000000001</v>
+        <v>453.6180000000001</v>
       </c>
       <c r="G100">
         <v>69</v>
@@ -9469,37 +9469,37 @@
         <v>49.86666666666667</v>
       </c>
       <c r="M100">
-        <v>90.16642880000002</v>
+        <v>91.08649440000001</v>
       </c>
       <c r="N100">
-        <v>-40.29976213333335</v>
+        <v>-41.21982773333333</v>
       </c>
       <c r="O100">
-        <v>-9.067446480000003</v>
+        <v>-9.274461240000001</v>
       </c>
       <c r="P100">
-        <v>-31.23231565333334</v>
+        <v>-31.94536649333333</v>
       </c>
       <c r="Q100">
-        <v>-24.43231565333334</v>
+        <v>-25.14536649333333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.842728980090834</v>
+        <v>5.639657960181668</v>
       </c>
       <c r="T100">
-        <v>19.50142664366773</v>
+        <v>39.00285328733546</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1244365574784747</v>
+        <v>0.1231796225544498</v>
       </c>
       <c r="W100">
-        <v>0.1758131392583223</v>
+        <v>0.1760655317910665</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5530513665709988</v>
+        <v>0.5474649891308878</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2307014560749726</v>
-      </c>
-      <c r="C101">
-        <v>-222.3791532088201</v>
-      </c>
-      <c r="D101">
-        <v>162.2388467911799</v>
-      </c>
-      <c r="E101">
-        <v>308.518</v>
-      </c>
-      <c r="F101">
-        <v>453.6180000000001</v>
-      </c>
-      <c r="G101">
-        <v>69</v>
-      </c>
-      <c r="H101">
-        <v>313.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>56.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>6.800000000000001</v>
-      </c>
-      <c r="L101">
-        <v>49.86666666666667</v>
-      </c>
-      <c r="M101">
-        <v>91.08649440000001</v>
-      </c>
-      <c r="N101">
-        <v>-41.21982773333333</v>
-      </c>
-      <c r="O101">
-        <v>-9.274461240000001</v>
-      </c>
-      <c r="P101">
-        <v>-31.94536649333333</v>
-      </c>
-      <c r="Q101">
-        <v>-25.14536649333333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.639657960181668</v>
-      </c>
-      <c r="T101">
-        <v>39.00285328733546</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1231796225544498</v>
-      </c>
-      <c r="W101">
-        <v>0.1760655317910665</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5474649891308878</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
